--- a/analisis/Analisis_Presupuesto_2026-09.xlsx
+++ b/analisis/Analisis_Presupuesto_2026-09.xlsx
@@ -3883,13 +3883,13 @@
     <t>% NP obras</t>
   </si>
   <si>
-    <t>V1 total</t>
-  </si>
-  <si>
-    <t>V2 total</t>
-  </si>
-  <si>
-    <t>Δ V4-V2</t>
+    <t>V1 obras+AIU</t>
+  </si>
+  <si>
+    <t>V2 obras+AIU</t>
+  </si>
+  <si>
+    <t>Δ obras V4-V2</t>
   </si>
   <si>
     <t>TOTAL 27 CIVs</t>
@@ -4036,6 +4036,24 @@
     <t>$/m² = $2,317,646 (2.27× mediana $1,019,119/m²). Obras con AIU = $3,950,103,092. Top 3 renglones: [5] CONTRATO 1752-2021 - BOX CULVERT PREFABRICADO TIPO 1, Ancho  $1,879,745,340; [2] LOSA DE CONCRETO MR45 (SUMINISTRO, FORMALETEADO, COLOCACIÓN, $556,140,139; [2] MEZCLA ASFÁLTICA EN CALIENTE DENSA MD19 CON CEMENTO ASFÁLTIC $121,429,566</t>
   </si>
   <si>
+    <t>H02-101</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>CIV 16000024 (KR 65A) con Δ obras $3,672,527,262</t>
+  </si>
+  <si>
+    <t>Obras iniciales $2,226,670,707 -&gt; finales $5,899,197,969. Delta = $3,672,527,262 (164.9%).</t>
+  </si>
+  <si>
+    <t>columnas del CIV</t>
+  </si>
+  <si>
+    <t>Solicitar justificacion tecnica del Δ por CIV con documentacion de campo y tramites IDU.</t>
+  </si>
+  <si>
     <t>H01-014</t>
   </si>
   <si>
@@ -4043,24 +4061,6 @@
   </si>
   <si>
     <t>2. PAVIMENTOS: valor inicial 15.328.367.366 -&gt; final 18.884.475.147. Balance mayores/menores 286.507.169 + incorporacion NP 3.269.600.612.</t>
-  </si>
-  <si>
-    <t>H02-101</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>CIV 16000024 (KR 65A) con Δ obras $3,369,431,763</t>
-  </si>
-  <si>
-    <t>Obras iniciales $2,529,766,206 -&gt; finales $5,899,197,969. Delta = $3,369,431,763 (133.2%).</t>
-  </si>
-  <si>
-    <t>columnas del CIV</t>
-  </si>
-  <si>
-    <t>Solicitar justificacion tecnica del Δ por CIV con documentacion de campo y tramites IDU.</t>
   </si>
   <si>
     <t>H01-035</t>
@@ -4205,6 +4205,15 @@
     <t>Item 1.012 'BASE GRANULAR CLASE A (BG_A) (SUMINISTRO, EXTENDIDO, NIVELACIÓN, HUMEDECIMIENTO Y COMPACTACIÓN CON VIBROCOMPACTADOR)' pasa de 7718.0 a 0 (M3). Reduccion -1.811.267.958.</t>
   </si>
   <si>
+    <t>H02-102</t>
+  </si>
+  <si>
+    <t>CIV 16000010 (CL18B) con Δ obras $1,658,490,306</t>
+  </si>
+  <si>
+    <t>Obras iniciales $2,291,612,786 -&gt; finales $3,950,103,092. Delta = $1,658,490,306 (72.4%).</t>
+  </si>
+  <si>
     <t>H01-016</t>
   </si>
   <si>
@@ -4232,91 +4241,82 @@
     <t>Item 3.039 'ANDEN CONCRETO GRAVA COMÚN DE 3000 PSI (210 KG/CM2) PREMEZCLADO E=0.10M (INCLUYE SUMINISTRO, FORMALETEO, FUNDIDA Y CURADO)': H=114.0, I=15468.629999999994 (M2), variacion relativa 13469%. Impacto 1.542.541.484.</t>
   </si>
   <si>
-    <t>H02-102</t>
-  </si>
-  <si>
-    <t>CIV 16000010 (CL18B) con Δ obras $1,497,959,062</t>
-  </si>
-  <si>
-    <t>Obras iniciales $2,452,144,030 -&gt; finales $3,950,103,092. Delta = $1,497,959,062 (61.1%).</t>
-  </si>
-  <si>
     <t>H02-103</t>
   </si>
   <si>
-    <t>CIV 500002375 (KR65) con Δ obras $1,486,799,059</t>
-  </si>
-  <si>
-    <t>Obras iniciales $0 -&gt; finales $1,486,799,059. Delta = $1,486,799,059 (0.0%).</t>
+    <t>CIV 16000017 (KR 65A) con Δ obras $1,325,793,518</t>
+  </si>
+  <si>
+    <t>Obras iniciales $1,441,265,454 -&gt; finales $2,767,058,972. Delta = $1,325,793,518 (92.0%).</t>
   </si>
   <si>
     <t>H02-104</t>
   </si>
   <si>
-    <t>CIV 16000013 (CL18B) con Δ obras $1,224,773,015</t>
-  </si>
-  <si>
-    <t>Obras iniciales $925,162,485 -&gt; finales $2,149,935,500. Delta = $1,224,773,015 (132.4%).</t>
+    <t>CIV 16000013 (CL18B) con Δ obras $1,321,707,331</t>
+  </si>
+  <si>
+    <t>Obras iniciales $828,228,169 -&gt; finales $2,149,935,500. Delta = $1,321,707,331 (159.6%).</t>
+  </si>
+  <si>
+    <t>H01-038</t>
+  </si>
+  <si>
+    <t>NP de alto valor (fila 87)</t>
+  </si>
+  <si>
+    <t>NP NP-16 'ESTAMPADO PARA CONCRETO MR DE POMPEYANOS, ACCESOS VEHICULARES A PREDIOS Y VÍAS (ACABADO Y CURADO, SUMINISTRO Y MANO DE OBRA. INCLUYE JUEGO DE MOLDES, COLOR ENDURECEDOR DE CUARZO, DESMOLDANTE EN POLVO COLOR, SELLADOR ACRÍLICO TRANSPARENTE SEMILUSTRE)' incorpora cantidad 18100.45 M2 por 1.107.150.225.</t>
+  </si>
+  <si>
+    <t>H01-025</t>
+  </si>
+  <si>
+    <t>Variacion relativa alta (fila 281)</t>
+  </si>
+  <si>
+    <t>Item 5.053 'TUBERIA CONCRETO ALTA RESISTENCIA D= 12" (INCLUYE SUMINISTRO, INSTALACIÓN Y MORTERO 2000 PSI PARA RECUBRIMIENTO DE JUNTA).': H=1945.0, I=0.0 (ML), variacion relativa 100%. Impacto -1.059.297.570.</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>H01-032</t>
+  </si>
+  <si>
+    <t>Item contractual eliminado (fila 281)</t>
+  </si>
+  <si>
+    <t>Item 5.053 'TUBERIA CONCRETO ALTA RESISTENCIA D= 12" (INCLUYE SUMINISTRO, INSTALACIÓN Y MORTERO 2000 PSI PARA RECUBRIMIENTO DE JUNTA).' pasa de 1945.0 a 0 (ML). Reduccion -1.059.297.570.</t>
+  </si>
+  <si>
+    <t>H01-026</t>
+  </si>
+  <si>
+    <t>Variacion relativa alta (fila 295)</t>
+  </si>
+  <si>
+    <t>Item 5.067 'SUMIDERO LATERAL SL-250A, H=1.7M (FUNDIDO EN SITIO, CONCRETO PREMEZCLADO. INCL. SUMIN, FORM, REF. Y CONSTR. INCL. TAPA)': H=123.0, I=0.0 (UN), variacion relativa 100%. Impacto -840.308.079.</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>H01-033</t>
+  </si>
+  <si>
+    <t>Item contractual eliminado (fila 295)</t>
+  </si>
+  <si>
+    <t>Item 5.067 'SUMIDERO LATERAL SL-250A, H=1.7M (FUNDIDO EN SITIO, CONCRETO PREMEZCLADO. INCL. SUMIN, FORM, REF. Y CONSTR. INCL. TAPA)' pasa de 123.0 a 0 (UN). Reduccion -840.308.079.</t>
   </si>
   <si>
     <t>H02-105</t>
   </si>
   <si>
-    <t>CIV 16000017 (KR 65A) con Δ obras $1,207,650,741</t>
-  </si>
-  <si>
-    <t>Obras iniciales $1,559,408,231 -&gt; finales $2,767,058,972. Delta = $1,207,650,741 (77.4%).</t>
-  </si>
-  <si>
-    <t>H01-038</t>
-  </si>
-  <si>
-    <t>NP de alto valor (fila 87)</t>
-  </si>
-  <si>
-    <t>NP NP-16 'ESTAMPADO PARA CONCRETO MR DE POMPEYANOS, ACCESOS VEHICULARES A PREDIOS Y VÍAS (ACABADO Y CURADO, SUMINISTRO Y MANO DE OBRA. INCLUYE JUEGO DE MOLDES, COLOR ENDURECEDOR DE CUARZO, DESMOLDANTE EN POLVO COLOR, SELLADOR ACRÍLICO TRANSPARENTE SEMILUSTRE)' incorpora cantidad 18100.45 M2 por 1.107.150.225.</t>
-  </si>
-  <si>
-    <t>H01-025</t>
-  </si>
-  <si>
-    <t>Variacion relativa alta (fila 281)</t>
-  </si>
-  <si>
-    <t>Item 5.053 'TUBERIA CONCRETO ALTA RESISTENCIA D= 12" (INCLUYE SUMINISTRO, INSTALACIÓN Y MORTERO 2000 PSI PARA RECUBRIMIENTO DE JUNTA).': H=1945.0, I=0.0 (ML), variacion relativa 100%. Impacto -1.059.297.570.</t>
-  </si>
-  <si>
-    <t>281</t>
-  </si>
-  <si>
-    <t>H01-032</t>
-  </si>
-  <si>
-    <t>Item contractual eliminado (fila 281)</t>
-  </si>
-  <si>
-    <t>Item 5.053 'TUBERIA CONCRETO ALTA RESISTENCIA D= 12" (INCLUYE SUMINISTRO, INSTALACIÓN Y MORTERO 2000 PSI PARA RECUBRIMIENTO DE JUNTA).' pasa de 1945.0 a 0 (ML). Reduccion -1.059.297.570.</t>
-  </si>
-  <si>
-    <t>H01-026</t>
-  </si>
-  <si>
-    <t>Variacion relativa alta (fila 295)</t>
-  </si>
-  <si>
-    <t>Item 5.067 'SUMIDERO LATERAL SL-250A, H=1.7M (FUNDIDO EN SITIO, CONCRETO PREMEZCLADO. INCL. SUMIN, FORM, REF. Y CONSTR. INCL. TAPA)': H=123.0, I=0.0 (UN), variacion relativa 100%. Impacto -840.308.079.</t>
-  </si>
-  <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>H01-033</t>
-  </si>
-  <si>
-    <t>Item contractual eliminado (fila 295)</t>
-  </si>
-  <si>
-    <t>Item 5.067 'SUMIDERO LATERAL SL-250A, H=1.7M (FUNDIDO EN SITIO, CONCRETO PREMEZCLADO. INCL. SUMIN, FORM, REF. Y CONSTR. INCL. TAPA)' pasa de 123.0 a 0 (UN). Reduccion -840.308.079.</t>
+    <t>CIV 9003980 (CL20) con Δ obras $801,161,445</t>
+  </si>
+  <si>
+    <t>Obras iniciales $1,773,268,906 -&gt; finales $2,574,430,351. Delta = $801,161,445 (45.2%).</t>
   </si>
   <si>
     <t>H01-039</t>
@@ -4509,6 +4509,21 @@
     <t>Solicitar al contratista trazabilidad documental del Fondo de Compensaciones: (1) que compensaciones especificas se planeaban financiar; (2) por que se retiraron; (3) verificar que no se este pagando doble via NPs de arqueologia u otros.</t>
   </si>
   <si>
+    <t>H02-001</t>
+  </si>
+  <si>
+    <t>Reparto de la linea base por CIV no publicado por el contratista</t>
+  </si>
+  <si>
+    <t>La col N del Excel suma $44,303,294,799 de valor inicial con AIU global. La reconstruccion por CIV (multiplicando cantidad_inicial_data_json * VU actualizado L) suma $41,842,985,108 (delta $-2,460,309,691). El Excel no reparte la cantidad contractual (col H) por CIV, por lo que la linea base por CIV se estima con data.json (contrato firmado); es un pixel-perfect solo para los ítems que mantuvieron el codigo_idu.</t>
+  </si>
+  <si>
+    <t>col H (linea base) vs bloque S:BW (matriz por CIV)</t>
+  </si>
+  <si>
+    <t>Pedir al contratista el reparto oficial de la cantidad contractual por CIV (col H desagregada) para auditar al peso el Delta por CIV.</t>
+  </si>
+  <si>
     <t>H03-NP-16000010</t>
   </si>
   <si>
@@ -4531,21 +4546,6 @@
   </si>
   <si>
     <t>Alinear hojas resumen/EJECUTIVO/Presupuesto estimado con el total final $75.426.575.199.</t>
-  </si>
-  <si>
-    <t>H02-001</t>
-  </si>
-  <si>
-    <t>Reparto de la linea base por CIV no publicado por el contratista</t>
-  </si>
-  <si>
-    <t>La col N del Excel suma $44,303,294,799 de valor inicial con AIU global. La reconstruccion por CIV (multiplicando cantidad_inicial_data_json * VU actualizado L) suma $45,408,291,095 (delta $1,104,996,296). El Excel no reparte la cantidad contractual (col H) por CIV, por lo que la linea base por CIV se estima con data.json (contrato firmado); es un pixel-perfect solo para los ítems que mantuvieron el codigo_idu.</t>
-  </si>
-  <si>
-    <t>col H (linea base) vs bloque S:BW (matriz por CIV)</t>
-  </si>
-  <si>
-    <t>Pedir al contratista el reparto oficial de la cantidad contractual por CIV (col H desagregada) para auditar al peso el Delta por CIV.</t>
   </si>
   <si>
     <t>H01-007</t>
@@ -41626,31 +41626,31 @@
         <v>2710.31</v>
       </c>
       <c r="F2" s="4">
-        <v>2180575896</v>
+        <v>1919271224</v>
       </c>
       <c r="G2" s="4">
         <v>2124569020</v>
       </c>
       <c r="H2" s="6">
-        <v>-56006876</v>
+        <v>205297796</v>
       </c>
       <c r="I2" s="9">
-        <v>-0.02568444240016492</v>
+        <v>0.1069665367941764</v>
       </c>
       <c r="J2" s="4">
-        <v>514701524</v>
+        <v>182289767</v>
       </c>
       <c r="K2" s="4">
-        <v>-263583532</v>
+        <v>-222416600</v>
       </c>
       <c r="L2" s="4">
         <v>413561201</v>
       </c>
       <c r="M2" s="4">
-        <v>245112989</v>
+        <v>627421749</v>
       </c>
       <c r="N2" s="4">
-        <v>-965799061</v>
+        <v>-795558323</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -41670,31 +41670,31 @@
         <v>2979.83</v>
       </c>
       <c r="F3" s="4">
-        <v>2590843256</v>
+        <v>2306495798</v>
       </c>
       <c r="G3" s="4">
         <v>2711308173</v>
       </c>
       <c r="H3" s="6">
-        <v>120464917</v>
+        <v>404812375</v>
       </c>
       <c r="I3" s="9">
-        <v>0.0464964125950196</v>
+        <v>0.175509695422389</v>
       </c>
       <c r="J3" s="4">
-        <v>775548964</v>
+        <v>285378781</v>
       </c>
       <c r="K3" s="4">
-        <v>-157602325</v>
+        <v>-123491728</v>
       </c>
       <c r="L3" s="4">
         <v>557275092</v>
       </c>
       <c r="M3" s="4">
-        <v>155739913</v>
+        <v>743291573</v>
       </c>
       <c r="N3" s="4">
-        <v>-1210496732</v>
+        <v>-1057641346</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -41714,31 +41714,31 @@
         <v>2373.61</v>
       </c>
       <c r="F4" s="4">
-        <v>2000370919</v>
+        <v>1773268906</v>
       </c>
       <c r="G4" s="4">
         <v>2574430351</v>
       </c>
       <c r="H4" s="6">
-        <v>574059432</v>
+        <v>801161445</v>
       </c>
       <c r="I4" s="9">
-        <v>0.2869764934830069</v>
+        <v>0.4517991841447199</v>
       </c>
       <c r="J4" s="4">
-        <v>915477285</v>
+        <v>373301602</v>
       </c>
       <c r="K4" s="4">
-        <v>-156078454</v>
+        <v>-91672565</v>
       </c>
       <c r="L4" s="4">
         <v>495791541</v>
       </c>
       <c r="M4" s="4">
-        <v>165564400</v>
+        <v>805675799</v>
       </c>
       <c r="N4" s="4">
-        <v>-846695344</v>
+        <v>-781934933</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -41758,31 +41758,31 @@
         <v>1404.75</v>
       </c>
       <c r="F5" s="4">
-        <v>1203121688</v>
+        <v>1050018340</v>
       </c>
       <c r="G5" s="4">
         <v>1632946727</v>
       </c>
       <c r="H5" s="6">
-        <v>429825039</v>
+        <v>582928387</v>
       </c>
       <c r="I5" s="9">
-        <v>0.357258158744122</v>
+        <v>0.5551601955828696</v>
       </c>
       <c r="J5" s="4">
-        <v>444159932</v>
+        <v>142657619</v>
       </c>
       <c r="K5" s="4">
-        <v>-67116219</v>
+        <v>-53109380</v>
       </c>
       <c r="L5" s="4">
         <v>353627844</v>
       </c>
       <c r="M5" s="4">
-        <v>254688876</v>
+        <v>606506584</v>
       </c>
       <c r="N5" s="4">
-        <v>-555535397</v>
+        <v>-466754282</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -41802,31 +41802,31 @@
         <v>1985.23</v>
       </c>
       <c r="F6" s="4">
-        <v>1688557241</v>
+        <v>1390366740</v>
       </c>
       <c r="G6" s="4">
         <v>2038357883</v>
       </c>
       <c r="H6" s="6">
-        <v>349800642</v>
+        <v>647991143</v>
       </c>
       <c r="I6" s="9">
-        <v>0.2071594811869336</v>
+        <v>0.4660577129455787</v>
       </c>
       <c r="J6" s="4">
-        <v>594990258</v>
+        <v>211844855</v>
       </c>
       <c r="K6" s="4">
-        <v>-148640673</v>
+        <v>-68113113</v>
       </c>
       <c r="L6" s="4">
         <v>460822231</v>
       </c>
       <c r="M6" s="4">
-        <v>204575736</v>
+        <v>720381837</v>
       </c>
       <c r="N6" s="4">
-        <v>-761946910</v>
+        <v>-676944668</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -41846,31 +41846,31 @@
         <v>2419.5</v>
       </c>
       <c r="F7" s="4">
-        <v>2032212311</v>
+        <v>1756193191</v>
       </c>
       <c r="G7" s="4">
         <v>2226451976</v>
       </c>
       <c r="H7" s="6">
-        <v>194239665</v>
+        <v>470258785</v>
       </c>
       <c r="I7" s="9">
-        <v>0.0955803997193677</v>
+        <v>0.2677716707990584</v>
       </c>
       <c r="J7" s="4">
-        <v>578686180</v>
+        <v>247663809</v>
       </c>
       <c r="K7" s="4">
-        <v>-190343822</v>
+        <v>-101923727</v>
       </c>
       <c r="L7" s="4">
         <v>484284632</v>
       </c>
       <c r="M7" s="4">
-        <v>183594962</v>
+        <v>607801137</v>
       </c>
       <c r="N7" s="4">
-        <v>-861982289</v>
+        <v>-767567066</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -41890,31 +41890,31 @@
         <v>1537.22</v>
       </c>
       <c r="F8" s="4">
-        <v>1275398199</v>
+        <v>1104610337</v>
       </c>
       <c r="G8" s="4">
         <v>1630625372</v>
       </c>
       <c r="H8" s="6">
-        <v>355227173</v>
+        <v>526015035</v>
       </c>
       <c r="I8" s="9">
-        <v>0.2785225612506922</v>
+        <v>0.4761996311102781</v>
       </c>
       <c r="J8" s="4">
-        <v>530283936</v>
+        <v>114389159</v>
       </c>
       <c r="K8" s="4">
-        <v>-95566730</v>
+        <v>-56363007</v>
       </c>
       <c r="L8" s="4">
         <v>385295483</v>
       </c>
       <c r="M8" s="4">
-        <v>185030711</v>
+        <v>667711315</v>
       </c>
       <c r="N8" s="4">
-        <v>-649816229</v>
+        <v>-585017918</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -41934,31 +41934,31 @@
         <v>1608.57</v>
       </c>
       <c r="F9" s="4">
-        <v>1393188525</v>
+        <v>1301940735</v>
       </c>
       <c r="G9" s="4">
         <v>1745875067</v>
       </c>
       <c r="H9" s="6">
-        <v>352686542</v>
+        <v>443934332</v>
       </c>
       <c r="I9" s="9">
-        <v>0.253150622239011</v>
+        <v>0.3409789094585784</v>
       </c>
       <c r="J9" s="4">
-        <v>633871620</v>
+        <v>399145087</v>
       </c>
       <c r="K9" s="4">
-        <v>-103525244</v>
+        <v>-56982908</v>
       </c>
       <c r="L9" s="4">
         <v>370902099</v>
       </c>
       <c r="M9" s="4">
-        <v>88332966</v>
+        <v>329611085</v>
       </c>
       <c r="N9" s="4">
-        <v>-636894899</v>
+        <v>-598741031</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -41978,31 +41978,31 @@
         <v>1045.93</v>
       </c>
       <c r="F10" s="4">
-        <v>675665665</v>
+        <v>638820344</v>
       </c>
       <c r="G10" s="4">
         <v>721728089</v>
       </c>
       <c r="H10" s="6">
-        <v>46062424</v>
+        <v>82907745</v>
       </c>
       <c r="I10" s="9">
-        <v>0.06817339756342362</v>
+        <v>0.1297825684148844</v>
       </c>
       <c r="J10" s="4">
-        <v>162277586</v>
+        <v>37365767</v>
       </c>
       <c r="K10" s="4">
-        <v>-15022963</v>
+        <v>-13415779</v>
       </c>
       <c r="L10" s="4">
         <v>170207808</v>
       </c>
       <c r="M10" s="4">
-        <v>121361491</v>
+        <v>264353875</v>
       </c>
       <c r="N10" s="4">
-        <v>-392761500</v>
+        <v>-375603926</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -42022,31 +42022,31 @@
         <v>2852</v>
       </c>
       <c r="F11" s="4">
-        <v>2447752810</v>
+        <v>2231841440</v>
       </c>
       <c r="G11" s="4">
         <v>2572153672</v>
       </c>
       <c r="H11" s="6">
-        <v>124400862</v>
+        <v>340312232</v>
       </c>
       <c r="I11" s="9">
-        <v>0.05082247745433086</v>
+        <v>0.1524804701179847</v>
       </c>
       <c r="J11" s="4">
-        <v>652546241</v>
+        <v>227331221</v>
       </c>
       <c r="K11" s="4">
-        <v>-378873345</v>
+        <v>-317302857</v>
       </c>
       <c r="L11" s="4">
         <v>762715918</v>
       </c>
       <c r="M11" s="4">
-        <v>108687432</v>
+        <v>587997617</v>
       </c>
       <c r="N11" s="4">
-        <v>-1020675384</v>
+        <v>-920429664</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -42066,31 +42066,31 @@
         <v>2544.68</v>
       </c>
       <c r="F12" s="4">
-        <v>2233910200</v>
+        <v>2073695190</v>
       </c>
       <c r="G12" s="4">
         <v>2347962590</v>
       </c>
       <c r="H12" s="6">
-        <v>114052390</v>
+        <v>274267400</v>
       </c>
       <c r="I12" s="9">
-        <v>0.05105504688594913</v>
+        <v>0.1322602286597385</v>
       </c>
       <c r="J12" s="4">
-        <v>712182732</v>
+        <v>304226839</v>
       </c>
       <c r="K12" s="4">
-        <v>-213007773</v>
+        <v>-169880963</v>
       </c>
       <c r="L12" s="4">
         <v>491988701</v>
       </c>
       <c r="M12" s="4">
-        <v>86718919</v>
+        <v>529038504</v>
       </c>
       <c r="N12" s="4">
-        <v>-963830193</v>
+        <v>-881105685</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -42110,31 +42110,31 @@
         <v>1704.36</v>
       </c>
       <c r="F13" s="4">
-        <v>2452144030</v>
+        <v>2291612786</v>
       </c>
       <c r="G13" s="4">
         <v>3950103092</v>
       </c>
       <c r="H13" s="6">
-        <v>1497959062</v>
+        <v>1658490306</v>
       </c>
       <c r="I13" s="9">
-        <v>0.6108772746109861</v>
+        <v>0.7237218766329575</v>
       </c>
       <c r="J13" s="4">
-        <v>580904806</v>
+        <v>224247396</v>
       </c>
       <c r="K13" s="4">
-        <v>-164803057</v>
+        <v>-111578051</v>
       </c>
       <c r="L13" s="4">
         <v>2308849811</v>
       </c>
       <c r="M13" s="4">
-        <v>230957312</v>
+        <v>665403854</v>
       </c>
       <c r="N13" s="4">
-        <v>-1457949812</v>
+        <v>-1428432706</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -42154,31 +42154,31 @@
         <v>1541.61</v>
       </c>
       <c r="F14" s="4">
-        <v>925162485</v>
+        <v>828228169</v>
       </c>
       <c r="G14" s="4">
         <v>2149935500</v>
       </c>
       <c r="H14" s="6">
-        <v>1224773015</v>
+        <v>1321707331</v>
       </c>
       <c r="I14" s="9">
-        <v>1.323846388994037</v>
+        <v>1.595825136684043</v>
       </c>
       <c r="J14" s="4">
-        <v>1187816132</v>
+        <v>861412774</v>
       </c>
       <c r="K14" s="4">
-        <v>-78332318</v>
+        <v>-44560484</v>
       </c>
       <c r="L14" s="4">
         <v>457445474</v>
       </c>
       <c r="M14" s="4">
-        <v>100461086</v>
+        <v>429247240</v>
       </c>
       <c r="N14" s="4">
-        <v>-442617358</v>
+        <v>-381837675</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -42198,31 +42198,31 @@
         <v>2402.99</v>
       </c>
       <c r="F15" s="4">
-        <v>2529766206</v>
+        <v>2226670707</v>
       </c>
       <c r="G15" s="4">
         <v>5899197969</v>
       </c>
       <c r="H15" s="6">
-        <v>3369431763</v>
+        <v>3672527262</v>
       </c>
       <c r="I15" s="9">
-        <v>1.331914291134301</v>
+        <v>1.649335597964553</v>
       </c>
       <c r="J15" s="4">
-        <v>3553283233</v>
+        <v>1670481233</v>
       </c>
       <c r="K15" s="4">
-        <v>-167532895</v>
+        <v>-97572926</v>
       </c>
       <c r="L15" s="4">
         <v>1016703547</v>
       </c>
       <c r="M15" s="4">
-        <v>179232750</v>
+        <v>2154675038</v>
       </c>
       <c r="N15" s="4">
-        <v>-1212254877</v>
+        <v>-1071759634</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -42242,31 +42242,31 @@
         <v>1361.36</v>
       </c>
       <c r="F16" s="4">
-        <v>1559408231</v>
+        <v>1441265454</v>
       </c>
       <c r="G16" s="4">
         <v>2767058972</v>
       </c>
       <c r="H16" s="6">
-        <v>1207650741</v>
+        <v>1325793518</v>
       </c>
       <c r="I16" s="9">
-        <v>0.7744288615339494</v>
+        <v>0.9198815626368299</v>
       </c>
       <c r="J16" s="4">
-        <v>1429617628</v>
+        <v>1062929957</v>
       </c>
       <c r="K16" s="4">
-        <v>-71778105</v>
+        <v>-48577593</v>
       </c>
       <c r="L16" s="4">
         <v>539293095</v>
       </c>
       <c r="M16" s="4">
-        <v>265375741</v>
+        <v>639108067</v>
       </c>
       <c r="N16" s="4">
-        <v>-954857623</v>
+        <v>-866960011</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -42286,31 +42286,31 @@
         <v>939.76</v>
       </c>
       <c r="F17" s="4">
-        <v>442631735</v>
+        <v>404749337</v>
       </c>
       <c r="G17" s="4">
         <v>812448409</v>
       </c>
       <c r="H17" s="6">
-        <v>369816674</v>
+        <v>407699072</v>
       </c>
       <c r="I17" s="9">
-        <v>0.8354951639425492</v>
+        <v>1.007287806872924</v>
       </c>
       <c r="J17" s="4">
-        <v>340112114</v>
+        <v>240435035</v>
       </c>
       <c r="K17" s="4">
-        <v>-20085657</v>
+        <v>-18585650</v>
       </c>
       <c r="L17" s="4">
         <v>140048966</v>
       </c>
       <c r="M17" s="4">
-        <v>116065926</v>
+        <v>218290421</v>
       </c>
       <c r="N17" s="4">
-        <v>-206324679</v>
+        <v>-172489705</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -42330,31 +42330,31 @@
         <v>2749.3</v>
       </c>
       <c r="F18" s="4">
-        <v>2399375386</v>
+        <v>2172680596</v>
       </c>
       <c r="G18" s="4">
         <v>2407629903</v>
       </c>
       <c r="H18" s="6">
-        <v>8254517</v>
+        <v>234949307</v>
       </c>
       <c r="I18" s="9">
-        <v>0.003440277435604234</v>
+        <v>0.108137987439365</v>
       </c>
       <c r="J18" s="4">
-        <v>621340374</v>
+        <v>231309119</v>
       </c>
       <c r="K18" s="4">
-        <v>-168884662</v>
+        <v>-95922976</v>
       </c>
       <c r="L18" s="4">
         <v>539949332</v>
       </c>
       <c r="M18" s="4">
-        <v>181902402</v>
+        <v>603647788</v>
       </c>
       <c r="N18" s="4">
-        <v>-1166052931</v>
+        <v>-1044033960</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -42374,31 +42374,31 @@
         <v>1593.8</v>
       </c>
       <c r="F19" s="4">
-        <v>1861384233</v>
+        <v>1711978189</v>
       </c>
       <c r="G19" s="4">
         <v>1624271261</v>
       </c>
       <c r="H19" s="6">
-        <v>-237112972</v>
+        <v>-87706928</v>
       </c>
       <c r="I19" s="9">
-        <v>-0.1273852909014084</v>
+        <v>-0.05123133493378869</v>
       </c>
       <c r="J19" s="4">
-        <v>429514160</v>
+        <v>139062675</v>
       </c>
       <c r="K19" s="4">
-        <v>-77623246</v>
+        <v>-49696086</v>
       </c>
       <c r="L19" s="4">
         <v>364120870</v>
       </c>
       <c r="M19" s="4">
-        <v>141467289</v>
+        <v>483716766</v>
       </c>
       <c r="N19" s="4">
-        <v>-1094592048</v>
+        <v>-1024911155</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -42418,31 +42418,31 @@
         <v>1791.31</v>
       </c>
       <c r="F20" s="4">
-        <v>1719244952</v>
+        <v>1504006937</v>
       </c>
       <c r="G20" s="4">
         <v>2190004906</v>
       </c>
       <c r="H20" s="6">
-        <v>470759954</v>
+        <v>685997969</v>
       </c>
       <c r="I20" s="9">
-        <v>0.2738178486156753</v>
+        <v>0.4561135671144846</v>
       </c>
       <c r="J20" s="4">
-        <v>650034311</v>
+        <v>172534203</v>
       </c>
       <c r="K20" s="4">
-        <v>-100617493</v>
+        <v>-49812815</v>
       </c>
       <c r="L20" s="4">
         <v>565653522</v>
       </c>
       <c r="M20" s="4">
-        <v>161319748</v>
+        <v>739488299</v>
       </c>
       <c r="N20" s="4">
-        <v>-805630136</v>
+        <v>-741865242</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -42462,31 +42462,31 @@
         <v>1519.4</v>
       </c>
       <c r="F21" s="4">
-        <v>1410865793</v>
+        <v>1236586250</v>
       </c>
       <c r="G21" s="4">
         <v>1790457295</v>
       </c>
       <c r="H21" s="6">
-        <v>379591502</v>
+        <v>553871045</v>
       </c>
       <c r="I21" s="9">
-        <v>0.2690486252366032</v>
+        <v>0.447903286163824</v>
       </c>
       <c r="J21" s="4">
-        <v>423496543</v>
+        <v>80214102</v>
       </c>
       <c r="K21" s="4">
-        <v>-79204911</v>
+        <v>-33865848</v>
       </c>
       <c r="L21" s="4">
         <v>536032431</v>
       </c>
       <c r="M21" s="4">
-        <v>188775290</v>
+        <v>622362254</v>
       </c>
       <c r="N21" s="4">
-        <v>-689507854</v>
+        <v>-650871898</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -42506,31 +42506,31 @@
         <v>1835.68</v>
       </c>
       <c r="F22" s="4">
-        <v>1754324624</v>
+        <v>1632752426</v>
       </c>
       <c r="G22" s="4">
         <v>1875405919</v>
       </c>
       <c r="H22" s="6">
-        <v>121081295</v>
+        <v>242653493</v>
       </c>
       <c r="I22" s="9">
-        <v>0.06901875134370798</v>
+        <v>0.1486162195419087</v>
       </c>
       <c r="J22" s="4">
-        <v>424085790</v>
+        <v>109958653</v>
       </c>
       <c r="K22" s="4">
-        <v>-121657192</v>
+        <v>-87754333</v>
       </c>
       <c r="L22" s="4">
         <v>393808491</v>
       </c>
       <c r="M22" s="4">
-        <v>307529837</v>
+        <v>649995927</v>
       </c>
       <c r="N22" s="4">
-        <v>-882685631</v>
+        <v>-823355245</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -42550,31 +42550,31 @@
         <v>1958.61</v>
       </c>
       <c r="F23" s="4">
-        <v>1868800216</v>
+        <v>1783508233</v>
       </c>
       <c r="G23" s="4">
         <v>1767518686</v>
       </c>
       <c r="H23" s="6">
-        <v>-101281530</v>
+        <v>-15989547</v>
       </c>
       <c r="I23" s="9">
-        <v>-0.0541960179225493</v>
+        <v>-0.008965221861131717</v>
       </c>
       <c r="J23" s="4">
-        <v>483801425</v>
+        <v>218285917</v>
       </c>
       <c r="K23" s="4">
-        <v>-92425803</v>
+        <v>-38185778</v>
       </c>
       <c r="L23" s="4">
         <v>378061014</v>
       </c>
       <c r="M23" s="4">
-        <v>101886725</v>
+        <v>459268542</v>
       </c>
       <c r="N23" s="4">
-        <v>-972604890</v>
+        <v>-1033419244</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -42594,31 +42594,31 @@
         <v>2644.76</v>
       </c>
       <c r="F24" s="4">
-        <v>2390907683</v>
+        <v>2230093561</v>
       </c>
       <c r="G24" s="4">
         <v>2560234587</v>
       </c>
       <c r="H24" s="6">
-        <v>169326904</v>
+        <v>330141026</v>
       </c>
       <c r="I24" s="9">
-        <v>0.07082118025884482</v>
+        <v>0.1480390920692856</v>
       </c>
       <c r="J24" s="4">
-        <v>779113868</v>
+        <v>321723334</v>
       </c>
       <c r="K24" s="4">
-        <v>-210727657</v>
+        <v>-127745345</v>
       </c>
       <c r="L24" s="4">
         <v>658093228</v>
       </c>
       <c r="M24" s="4">
-        <v>92563777</v>
+        <v>612681062</v>
       </c>
       <c r="N24" s="4">
-        <v>-1149716311</v>
+        <v>-1134611255</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -42638,31 +42638,31 @@
         <v>1996.95</v>
       </c>
       <c r="F25" s="4">
-        <v>1483775372</v>
+        <v>1289824581</v>
       </c>
       <c r="G25" s="4">
         <v>1789265635</v>
       </c>
       <c r="H25" s="6">
-        <v>305490263</v>
+        <v>499441054</v>
       </c>
       <c r="I25" s="9">
-        <v>0.2058871368030767</v>
+        <v>0.3872162628601664</v>
       </c>
       <c r="J25" s="4">
-        <v>637064581</v>
+        <v>221529676</v>
       </c>
       <c r="K25" s="4">
-        <v>-99185119</v>
+        <v>-44765975</v>
       </c>
       <c r="L25" s="4">
         <v>361958674</v>
       </c>
       <c r="M25" s="4">
-        <v>97967200</v>
+        <v>576800242</v>
       </c>
       <c r="N25" s="4">
-        <v>-692315071</v>
+        <v>-616081563</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -42682,31 +42682,31 @@
         <v>1159.92</v>
       </c>
       <c r="F26" s="4">
-        <v>0</v>
+        <v>923268542</v>
       </c>
       <c r="G26" s="4">
         <v>1486799059</v>
       </c>
       <c r="H26" s="6">
-        <v>1486799059</v>
+        <v>563530517</v>
       </c>
       <c r="I26" s="9">
-        <v>0</v>
+        <v>0.6103646895401317</v>
       </c>
       <c r="J26" s="4">
-        <v>0</v>
+        <v>280116868</v>
       </c>
       <c r="K26" s="4">
-        <v>0</v>
+        <v>-44777939</v>
       </c>
       <c r="L26" s="4">
         <v>307803002</v>
       </c>
       <c r="M26" s="4">
-        <v>1178996057</v>
+        <v>420882047</v>
       </c>
       <c r="N26" s="4">
-        <v>0</v>
+        <v>-400493465</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -42726,31 +42726,31 @@
         <v>2387.64</v>
       </c>
       <c r="F27" s="4">
-        <v>1742382373</v>
+        <v>1665738688</v>
       </c>
       <c r="G27" s="4">
         <v>1701875688</v>
       </c>
       <c r="H27" s="6">
-        <v>-40506685</v>
+        <v>36137000</v>
       </c>
       <c r="I27" s="9">
-        <v>-0.02324787350221891</v>
+        <v>0.02169427909691439</v>
       </c>
       <c r="J27" s="4">
-        <v>545915045</v>
+        <v>177888720</v>
       </c>
       <c r="K27" s="4">
-        <v>-239284049</v>
+        <v>-181783221</v>
       </c>
       <c r="L27" s="4">
         <v>351895379</v>
       </c>
       <c r="M27" s="4">
-        <v>72688895</v>
+        <v>497322644</v>
       </c>
       <c r="N27" s="4">
-        <v>-771721953</v>
+        <v>-809186522</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -42770,31 +42770,31 @@
         <v>1237.01</v>
       </c>
       <c r="F28" s="4">
-        <v>1146521066</v>
+        <v>953498407</v>
       </c>
       <c r="G28" s="4">
         <v>1098318068</v>
       </c>
       <c r="H28" s="6">
-        <v>-48202998</v>
+        <v>144819661</v>
       </c>
       <c r="I28" s="9">
-        <v>-0.0420428367427834</v>
+        <v>0.1518824362335825</v>
       </c>
       <c r="J28" s="4">
-        <v>292738505</v>
+        <v>140554724</v>
       </c>
       <c r="K28" s="4">
-        <v>-127836946</v>
+        <v>-156424699</v>
       </c>
       <c r="L28" s="4">
         <v>284735171</v>
       </c>
       <c r="M28" s="4">
-        <v>103461185</v>
+        <v>301003547</v>
       </c>
       <c r="N28" s="4">
-        <v>-601300913</v>
+        <v>-425049082</v>
       </c>
     </row>
   </sheetData>
@@ -42896,7 +42896,7 @@
         <v>1015959</v>
       </c>
       <c r="K2" s="9">
-        <v>19.47</v>
+        <v>0.1947</v>
       </c>
       <c r="L2" s="4">
         <v>2679612302</v>
@@ -42905,7 +42905,7 @@
         <v>2340063114</v>
       </c>
       <c r="N2" s="6">
-        <v>413500595</v>
+        <v>-215494094</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -42940,7 +42940,7 @@
         <v>1179266</v>
       </c>
       <c r="K3" s="9">
-        <v>20.55</v>
+        <v>0.2055</v>
       </c>
       <c r="L3" s="4">
         <v>2537825825</v>
@@ -42949,7 +42949,7 @@
         <v>2667336411</v>
       </c>
       <c r="N3" s="6">
-        <v>846675005</v>
+        <v>43971762</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -42984,7 +42984,7 @@
         <v>1405711</v>
       </c>
       <c r="K4" s="9">
-        <v>19.26</v>
+        <v>0.1926</v>
       </c>
       <c r="L4" s="4">
         <v>2312874652</v>
@@ -42993,7 +42993,7 @@
         <v>2444643007</v>
       </c>
       <c r="N4" s="6">
-        <v>891966875</v>
+        <v>129787344</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -43028,7 +43028,7 @@
         <v>1506598</v>
       </c>
       <c r="K5" s="9">
-        <v>21.66</v>
+        <v>0.2166</v>
       </c>
       <c r="L5" s="4">
         <v>1424778297</v>
@@ -43037,7 +43037,7 @@
         <v>1538753791</v>
       </c>
       <c r="N5" s="6">
-        <v>577639136</v>
+        <v>94192936</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -43072,7 +43072,7 @@
         <v>1330742</v>
       </c>
       <c r="K6" s="9">
-        <v>22.61</v>
+        <v>0.2261</v>
       </c>
       <c r="L6" s="4">
         <v>1972706135</v>
@@ -43081,7 +43081,7 @@
         <v>2041220357</v>
       </c>
       <c r="N6" s="6">
-        <v>600608758</v>
+        <v>-2862474</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -43116,7 +43116,7 @@
         <v>1192647</v>
       </c>
       <c r="K7" s="9">
-        <v>21.75</v>
+        <v>0.2175</v>
       </c>
       <c r="L7" s="4">
         <v>1850363381</v>
@@ -43125,7 +43125,7 @@
         <v>2075372979</v>
       </c>
       <c r="N7" s="6">
-        <v>810236904</v>
+        <v>151078997</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -43160,7 +43160,7 @@
         <v>1374809</v>
       </c>
       <c r="K8" s="9">
-        <v>23.63</v>
+        <v>0.2363</v>
       </c>
       <c r="L8" s="4">
         <v>1767059390</v>
@@ -43169,7 +43169,7 @@
         <v>1856888679</v>
       </c>
       <c r="N8" s="6">
-        <v>256495638</v>
+        <v>-226263307</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -43204,7 +43204,7 @@
         <v>1406687</v>
       </c>
       <c r="K9" s="9">
-        <v>21.24</v>
+        <v>0.2124</v>
       </c>
       <c r="L9" s="4">
         <v>1157651934</v>
@@ -43213,7 +43213,7 @@
         <v>1299966980</v>
       </c>
       <c r="N9" s="6">
-        <v>962787574</v>
+        <v>445908087</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -43248,7 +43248,7 @@
         <v>894325</v>
       </c>
       <c r="K10" s="9">
-        <v>23.58</v>
+        <v>0.2358</v>
       </c>
       <c r="L10" s="4">
         <v>696444456</v>
@@ -43257,7 +43257,7 @@
         <v>815380689</v>
       </c>
       <c r="N10" s="6">
-        <v>120020447</v>
+        <v>-93652600</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -43292,7 +43292,7 @@
         <v>1168885</v>
       </c>
       <c r="K11" s="9">
-        <v>29.65</v>
+        <v>0.2965</v>
       </c>
       <c r="L11" s="4">
         <v>2751554997</v>
@@ -43301,7 +43301,7 @@
         <v>2880817470</v>
       </c>
       <c r="N11" s="6">
-        <v>452841705</v>
+        <v>-308663798</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -43336,7 +43336,7 @@
         <v>1195865</v>
       </c>
       <c r="K12" s="9">
-        <v>20.95</v>
+        <v>0.2095</v>
       </c>
       <c r="L12" s="4">
         <v>2226684665</v>
@@ -43345,7 +43345,7 @@
         <v>2358154014</v>
       </c>
       <c r="N12" s="6">
-        <v>684940617</v>
+        <v>-10191424</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -43380,7 +43380,7 @@
         <v>3003803</v>
       </c>
       <c r="K13" s="9">
-        <v>58.45</v>
+        <v>0.5845</v>
       </c>
       <c r="L13" s="4">
         <v>1704354625</v>
@@ -43389,7 +43389,7 @@
         <v>3827888648</v>
       </c>
       <c r="N13" s="6">
-        <v>1291672270</v>
+        <v>122214444</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -43424,7 +43424,7 @@
         <v>1807487</v>
       </c>
       <c r="K14" s="9">
-        <v>21.28</v>
+        <v>0.2128</v>
       </c>
       <c r="L14" s="4">
         <v>1893852881</v>
@@ -43433,7 +43433,7 @@
         <v>1258518912</v>
       </c>
       <c r="N14" s="6">
-        <v>1527921215</v>
+        <v>891416588</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -43468,7 +43468,7 @@
         <v>3181744</v>
       </c>
       <c r="K15" s="9">
-        <v>17.23</v>
+        <v>0.1723</v>
       </c>
       <c r="L15" s="4">
         <v>3752120822</v>
@@ -43477,7 +43477,7 @@
         <v>4238174174</v>
       </c>
       <c r="N15" s="6">
-        <v>3407525866</v>
+        <v>1661023795</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -43512,7 +43512,7 @@
         <v>2634327</v>
       </c>
       <c r="K16" s="9">
-        <v>19.49</v>
+        <v>0.1949</v>
       </c>
       <c r="L16" s="4">
         <v>1533890165</v>
@@ -43521,7 +43521,7 @@
         <v>1888172582</v>
       </c>
       <c r="N16" s="6">
-        <v>1698095078</v>
+        <v>878886390</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -43556,7 +43556,7 @@
         <v>1120477</v>
       </c>
       <c r="K17" s="9">
-        <v>17.24</v>
+        <v>0.1724</v>
       </c>
       <c r="L17" s="4">
         <v>585887485</v>
@@ -43565,7 +43565,7 @@
         <v>785835853</v>
       </c>
       <c r="N17" s="6">
-        <v>267144038</v>
+        <v>26612556</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -43600,7 +43600,7 @@
         <v>1134990</v>
       </c>
       <c r="K18" s="9">
-        <v>22.43</v>
+        <v>0.2243</v>
       </c>
       <c r="L18" s="4">
         <v>2048902433</v>
@@ -43609,7 +43609,7 @@
         <v>2205169960</v>
       </c>
       <c r="N18" s="6">
-        <v>915256943</v>
+        <v>202459943</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -43644,7 +43644,7 @@
         <v>1320836</v>
       </c>
       <c r="K19" s="9">
-        <v>22.42</v>
+        <v>0.2242</v>
       </c>
       <c r="L19" s="4">
         <v>1512963553</v>
@@ -43653,7 +43653,7 @@
         <v>1822060696</v>
       </c>
       <c r="N19" s="6">
-        <v>283088328</v>
+        <v>-197789435</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -43688,7 +43688,7 @@
         <v>1584523</v>
       </c>
       <c r="K20" s="9">
-        <v>25.83</v>
+        <v>0.2583</v>
       </c>
       <c r="L20" s="4">
         <v>2087411444</v>
@@ -43697,7 +43697,7 @@
         <v>2168192162</v>
       </c>
       <c r="N20" s="6">
-        <v>670180221</v>
+        <v>21812744</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -43732,7 +43732,7 @@
         <v>1527271</v>
       </c>
       <c r="K21" s="9">
-        <v>29.94</v>
+        <v>0.2994</v>
       </c>
       <c r="L21" s="4">
         <v>1815561841</v>
@@ -43741,7 +43741,7 @@
         <v>1928040404</v>
       </c>
       <c r="N21" s="6">
-        <v>392495283</v>
+        <v>-137583109</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -43776,7 +43776,7 @@
         <v>1324106</v>
       </c>
       <c r="K22" s="9">
-        <v>21</v>
+        <v>0.21</v>
       </c>
       <c r="L22" s="4">
         <v>1643316068</v>
@@ -43785,7 +43785,7 @@
         <v>2104600859</v>
       </c>
       <c r="N22" s="6">
-        <v>326033133</v>
+        <v>-229194940</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -43820,7 +43820,7 @@
         <v>1169608</v>
       </c>
       <c r="K23" s="9">
-        <v>21.39</v>
+        <v>0.2139</v>
       </c>
       <c r="L23" s="4">
         <v>1639392473</v>
@@ -43829,7 +43829,7 @@
         <v>2096946548</v>
       </c>
       <c r="N23" s="6">
-        <v>193859382</v>
+        <v>-329427862</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -43864,7 +43864,7 @@
         <v>1254636</v>
       </c>
       <c r="K24" s="9">
-        <v>25.7</v>
+        <v>0.257</v>
       </c>
       <c r="L24" s="4">
         <v>1939975267</v>
@@ -43873,7 +43873,7 @@
         <v>2167849792</v>
       </c>
       <c r="N24" s="6">
-        <v>1150361563</v>
+        <v>392384795</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -43908,7 +43908,7 @@
         <v>1161267</v>
       </c>
       <c r="K25" s="9">
-        <v>20.23</v>
+        <v>0.2023</v>
       </c>
       <c r="L25" s="4">
         <v>1682838531</v>
@@ -43917,7 +43917,7 @@
         <v>1796568803</v>
       </c>
       <c r="N25" s="6">
-        <v>522422424</v>
+        <v>-7303168</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -43952,7 +43952,7 @@
         <v>1661302</v>
       </c>
       <c r="K26" s="9">
-        <v>20.7</v>
+        <v>0.207</v>
       </c>
       <c r="L26" s="4">
         <v>1414104748</v>
@@ -43961,7 +43961,7 @@
         <v>1565392676</v>
       </c>
       <c r="N26" s="6">
-        <v>361584463</v>
+        <v>-78593617</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -43996,7 +43996,7 @@
         <v>923811</v>
       </c>
       <c r="K27" s="9">
-        <v>20.68</v>
+        <v>0.2068</v>
       </c>
       <c r="L27" s="4">
         <v>1743449483</v>
@@ -44005,7 +44005,7 @@
         <v>1950567933</v>
       </c>
       <c r="N27" s="6">
-        <v>255160894</v>
+        <v>-248692245</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -44040,7 +44040,7 @@
         <v>1150745</v>
       </c>
       <c r="K28" s="9">
-        <v>25.92</v>
+        <v>0.2592</v>
       </c>
       <c r="L28" s="4">
         <v>1097565022</v>
@@ -44049,7 +44049,7 @@
         <v>1159443953</v>
       </c>
       <c r="N28" s="6">
-        <v>264039466</v>
+        <v>-61125885</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -45012,54 +45012,54 @@
         <v>1308</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1321</v>
+        <v>1336</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1324</v>
+        <v>1339</v>
       </c>
       <c r="H7" s="4">
-        <v>3556107781</v>
+        <v>3672527262</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1325</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1339</v>
+        <v>1321</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1342</v>
+        <v>1324</v>
       </c>
       <c r="H8" s="4">
-        <v>3369431763</v>
+        <v>3556107781</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1343</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -45447,7 +45447,7 @@
         <v>1308</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1321</v>
+        <v>1336</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>1392</v>
@@ -45459,13 +45459,13 @@
         <v>1312</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1324</v>
+        <v>1339</v>
       </c>
       <c r="H22" s="4">
-        <v>1613831550</v>
+        <v>1658490306</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>1325</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -45488,13 +45488,13 @@
         <v>1312</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>944</v>
+        <v>1324</v>
       </c>
       <c r="H23" s="4">
-        <v>1542541484</v>
+        <v>1613831550</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1373</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -45523,7 +45523,7 @@
         <v>1542541484</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1362</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -45534,7 +45534,7 @@
         <v>1308</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1339</v>
+        <v>1321</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>1401</v>
@@ -45546,13 +45546,13 @@
         <v>1312</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1342</v>
+        <v>944</v>
       </c>
       <c r="H25" s="4">
-        <v>1497959062</v>
+        <v>1542541484</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1343</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -45563,7 +45563,7 @@
         <v>1308</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>1404</v>
@@ -45575,13 +45575,13 @@
         <v>1312</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="H26" s="4">
-        <v>1486799059</v>
+        <v>1325793518</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -45592,7 +45592,7 @@
         <v>1308</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>1407</v>
@@ -45604,13 +45604,13 @@
         <v>1312</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="H27" s="4">
-        <v>1224773015</v>
+        <v>1321707331</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -45621,7 +45621,7 @@
         <v>1308</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1339</v>
+        <v>1321</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>1410</v>
@@ -45633,13 +45633,13 @@
         <v>1312</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1342</v>
+        <v>945</v>
       </c>
       <c r="H28" s="4">
-        <v>1207650741</v>
+        <v>1107150225</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -45662,18 +45662,18 @@
         <v>1312</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>945</v>
+        <v>1415</v>
       </c>
       <c r="H29" s="4">
-        <v>1107150225</v>
+        <v>-1059297570</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>1347</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="2" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>1308</v>
@@ -45682,22 +45682,22 @@
         <v>1321</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="H30" s="4">
         <v>-1059297570</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -45720,18 +45720,18 @@
         <v>1312</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="H31" s="4">
-        <v>-1059297570</v>
+        <v>-840308079</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="2" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>1308</v>
@@ -45740,22 +45740,22 @@
         <v>1321</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="H32" s="4">
         <v>-840308079</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -45766,7 +45766,7 @@
         <v>1308</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1321</v>
+        <v>1336</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>1427</v>
@@ -45778,13 +45778,13 @@
         <v>1312</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1425</v>
+        <v>1339</v>
       </c>
       <c r="H33" s="4">
-        <v>-840308079</v>
+        <v>801161445</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>1366</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -46226,7 +46226,7 @@
         <v>1481</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1327</v>
+        <v>1336</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>1493</v>
@@ -46238,64 +46238,64 @@
         <v>1312</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1330</v>
+        <v>1495</v>
       </c>
       <c r="H49" s="4">
-        <v>2308849811</v>
+        <v>2460309691</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="2" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>1481</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1468</v>
+        <v>1327</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1498</v>
-      </c>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
+        <v>1499</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>1330</v>
+      </c>
       <c r="H50" s="4">
-        <v>1988375733</v>
+        <v>2308849811</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="2" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>1481</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1339</v>
+        <v>1468</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1502</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>1312</v>
-      </c>
-      <c r="G51" s="2" t="s">
         <v>1503</v>
       </c>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
       <c r="H51" s="4">
-        <v>1104996296</v>
+        <v>1988375733</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>1504</v>
@@ -46541,7 +46541,7 @@
         <v>1481</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>1535</v>
@@ -46553,7 +46553,7 @@
         <v>1312</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="H60" s="4">
         <v>0</v>
@@ -46570,7 +46570,7 @@
         <v>1481</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>1539</v>
@@ -46582,7 +46582,7 @@
         <v>1312</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="H61" s="4">
         <v>0</v>
@@ -46829,7 +46829,7 @@
         <v>1559</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>1578</v>

--- a/analisis/Analisis_Presupuesto_2026-09.xlsx
+++ b/analisis/Analisis_Presupuesto_2026-09.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Costo por CIV'!$A$1:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hallazgos!$A$1:$I$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hallazgos!$A$1:$I$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">NPs!$A$1:$L$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Variación neta por código'!$A$1:$F$267</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Variación por CIV'!$A$1:$N$28</definedName>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5380" uniqueCount="1588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5388" uniqueCount="1594">
   <si>
     <t>Análisis Presupuesto 01-09-2026 · 75MM · 8 meses</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Fecha del análisis:</t>
   </si>
   <si>
-    <t>2026-09-27</t>
+    <t>2026-09-28</t>
   </si>
   <si>
     <t>Contratista:</t>
@@ -3970,7 +3970,7 @@
     <t>PRESUPUESTO TODOS LOS CIV 84 NP</t>
   </si>
   <si>
-    <t>679-680</t>
+    <t>675-676</t>
   </si>
   <si>
     <t>Documentar formalmente en la comunicacion oficial que la reduccion del capitulo 7 en V4 no representa un ahorro sino una reclasificacion. Solicitar al contratista una tabla de conciliacion V2-V4 por capitulo antes de proceder con cualquier aprobacion de adicion.</t>
@@ -3989,6 +3989,27 @@
   </si>
   <si>
     <t>Solicitar al contratista: (1) cronograma semana a semana con curvas S y frentes de obra activos simultaneos; (2) certificaciones de facturacion mensual de los ultimos 24 meses; (3) plan de recursos (personal, equipo, subcontratistas) que soporte el ritmo triplicado; (4) analisis de riesgo de incumplimiento con matriz de contingencia.</t>
+  </si>
+  <si>
+    <t>H04</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Los VU de V4 estan +49.0% (mediana) sobre los VU pactados en la propuesta: 15.086.222.761 con AIU a cantidades finales</t>
+  </si>
+  <si>
+    <t>469 renglones contractuales tienen VU pactado (col M de PRESUPUESTO CONTRACTUAL MAYO 25). Valorados al VU pactado valdrian 28.959.881.218 en vez de 44.046.009.245. El valor actual de obras del contrato (N688 = 44.303.294.799) ya esta calculado con los VU de V4 sobre las cantidades contractuales, asi que la actualizacion de precios (a insumos VISOR 13-09-2024) se formalizo antes de esta solicitud; el presupuesto original de la propuesta (fila 246 col O) era 28.420.960.042 de obras y 50.793.789.333 en total. Top impacto: 7785 fila 34 +76.0%, 6016 fila 20 +39.7%, 3017 fila 14 +32.5%, 5182 fila 531 +48.0%, 3425 fila 85 +50.6%</t>
+  </si>
+  <si>
+    <t>PRESUPUESTO CONTRACTUAL MAYO 25</t>
+  </si>
+  <si>
+    <t>246, 279 y col M</t>
+  </si>
+  <si>
+    <t>Pedir el otrosi o acta que autorizo actualizar los VU pactados a insumos 13-09-2024 y confirmar si ese incremento se contabilizo como adicion (cuenta para el tope del 50% del art. 40 de la Ley 80) o como reajuste.</t>
   </si>
   <si>
     <t>H01-013</t>
@@ -4076,21 +4097,6 @@
     <t>Revisar aprobacion IDU del NP, analisis de precio unitario y sustento tecnico. Verificar que no exista un item contractual equivalente.</t>
   </si>
   <si>
-    <t>H06-01</t>
-  </si>
-  <si>
-    <t>Riesgo de doble pago en acero por 2.977M-3.053M</t>
-  </si>
-  <si>
-    <t>En V4 coexisten (a) los items reales de acero cargados dentro de obras+AIU sumando 3.052.987.517 (filas 685-690) y (b) la bolsa fija F Actividades Acero de 2.977.517.840 (fila 701) que no se modifica desde V0. La suma total pagable de acero seria 6.030.505.357, lo cual es inconsistente con el diseno estructural (memorias de la hoja Aceros muestran ~2.500M en cantidades teoricas).</t>
-  </si>
-  <si>
-    <t>685-690 y 701</t>
-  </si>
-  <si>
-    <t>Exigir al contratista aclaracion escrita: si la bolsa F se pagara adicional al costo de los items reales, presentar sustento tecnico de esa duplicidad. En caso contrario, descontar la bolsa F del pago cuando se pagan los items reales de acero para evitar doble facturacion.</t>
-  </si>
-  <si>
     <t>H01-015</t>
   </si>
   <si>
@@ -4437,9 +4443,6 @@
     <t>H01</t>
   </si>
   <si>
-    <t>04</t>
-  </si>
-  <si>
     <t>Inconsistencias aritmeticas en columnas M/N/O/Q (2 filas)</t>
   </si>
   <si>
@@ -4449,337 +4452,352 @@
     <t>Solicitar re-calculo de columnas M/N/O/Q con formulas. Detectar filas de digitacion manual.</t>
   </si>
   <si>
+    <t>H03</t>
+  </si>
+  <si>
+    <t>VU V4 desviado &gt;2% de la referencia APU actualizado 13-09-2024 (367 renglones)</t>
+  </si>
+  <si>
+    <t>Referencia: columna Q 'VALOR ITEM COSTO DIRECTO ACTUALIZACION DE APU INSUMOS VISOR 13-09-2024' de la hoja PRESUPUESTO CONTRACTUAL MAYO 25 (es el 'precio original' del dashboard). Top: 4878 70.52%, 4878 70.52%, 4878 70.52%, 4878 70.52%, 8406 42.0%</t>
+  </si>
+  <si>
+    <t>Pedir el APU (FO-GI-19) de cada renglon con VU distinto a la referencia y la autorizacion del IDU para usarlo en la adicion.</t>
+  </si>
+  <si>
+    <t>H06-05</t>
+  </si>
+  <si>
+    <t>MEDIA</t>
+  </si>
+  <si>
+    <t>Salto V3 (63MM, 3 meses) a V4 (75MM, 8 meses) implica delta de $11.677M</t>
+  </si>
+  <si>
+    <t>En 4 meses (mayo a septiembre 2026) el presupuesto adicional pedido paso de $4.323M (V3) a $16.000M (V4), un incremento de $11.677M. El 88,7% del delta se explica por obras (+$10.361M) y el 11,3% por escalar SST/PGS/PMT de 3 a 8 meses. Los VU (precios unitarios) son practicamente identicos entre V3 y V4, por lo que el delta es efecto CANTIDAD y NPs, no efecto PRECIO.</t>
+  </si>
+  <si>
+    <t>PRESUPUESTO 63 mm vs PRESUPUESTO TODOS LOS CIV 84 NP</t>
+  </si>
+  <si>
+    <t>652 (63 mm) y 688</t>
+  </si>
+  <si>
+    <t>Solicitar al contratista la sustentacion tecnica del incremento de $10.361M en obras entre V3 y V4: (1) que items se incorporaron o crecieron; (2) que NPs se agregaron; (3) por que no se identificaron en V3 (mayo 2026) y aparecen 4 meses despues. Verificar contra memorias de cantidades y bitacora de obra.</t>
+  </si>
+  <si>
+    <t>H06-06</t>
+  </si>
+  <si>
+    <t>El Fondo de Compensaciones aparecio en V2 y desaparecio en V4 sin trazabilidad</t>
+  </si>
+  <si>
+    <t>V2 (Alt 1, 21-04-2026) incluyo un Fondo de Compensaciones de 5.942.657.520 que no existe ni en V0 ni en V4. En V3 y V4 vuelve a 0. No hay comunicacion oficial que explique el origen ni el motivo de su retiro. Podria estar relacionado con compensaciones ambientales/arqueologicas que se movieron a los NP-109 y NP-110 (arqueologia GLB/MES) que aparecen ahora dentro de obras.</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>Solicitar al contratista trazabilidad documental del Fondo de Compensaciones: (1) que compensaciones especificas se planeaban financiar; (2) por que se retiraron; (3) verificar que no se este pagando doble via NPs de arqueologia u otros.</t>
+  </si>
+  <si>
+    <t>H02-001</t>
+  </si>
+  <si>
+    <t>Reparto de la linea base por CIV no publicado por el contratista</t>
+  </si>
+  <si>
+    <t>La col N del Excel suma $44,303,294,799 de valor inicial con AIU global. La reconstruccion por CIV (multiplicando cantidad_inicial_data_json * VU actualizado L) suma $41,842,985,108 (delta $-2,460,309,691). El Excel no reparte la cantidad contractual (col H) por CIV, por lo que la linea base por CIV se estima con data.json (contrato firmado); es un pixel-perfect solo para los ítems que mantuvieron el codigo_idu.</t>
+  </si>
+  <si>
+    <t>col H (linea base) vs bloque S:BW (matriz por CIV)</t>
+  </si>
+  <si>
+    <t>Pedir al contratista el reparto oficial de la cantidad contractual por CIV (col H desagregada) para auditar al peso el Delta por CIV.</t>
+  </si>
+  <si>
+    <t>H03-NP-16000010</t>
+  </si>
+  <si>
+    <t>CIV 16000010: 58.45% del valor viene de NPs</t>
+  </si>
+  <si>
+    <t>Contractual $1,641,253,281 + NP $2,308,849,811 = obras totales. Alta dependencia de precios no pactados.</t>
+  </si>
+  <si>
+    <t>Auditar NPs asignados a este CIV, verificar códigos IDU, análisis de precios unitarios y actas de fijación.</t>
+  </si>
+  <si>
+    <t>H01-007</t>
+  </si>
+  <si>
+    <t>Salto extremo de cantidad (I/H = 39.9949x) - fila 73</t>
+  </si>
+  <si>
+    <t>Item 3.027 'SARDINEL FUNDIDO EN SITIO EN CONCRETO PREMEZCLADO DE 3000PSI. SUMINISTRO Y CONSTRUCCION. (GRAVA COMÚN) E=0.20M H=0.35M (INCLUYE FORMALETA METÁLICA, ACERO DE REFUERZO Y ALAMBRE NEGRO).' paso de 141.0 a 5639.28 ML. Impacto 413.740.072.</t>
+  </si>
+  <si>
+    <t>H01-018</t>
+  </si>
+  <si>
+    <t>Variacion capitulo 7. DESVÍOS: -326.577.225</t>
+  </si>
+  <si>
+    <t>7. DESVÍOS: valor inicial 326.577.225 -&gt; final 0. Balance mayores/menores -326.577.225 + incorporacion NP 0.</t>
+  </si>
+  <si>
+    <t>H01-003</t>
+  </si>
+  <si>
+    <t>Posible reemplazo contractual-&gt;NP (filas 489 -&gt; 551)</t>
+  </si>
+  <si>
+    <t>Item contractual '6.006 - 2 DUCTOS D=3" PVC-EB (INCLUYE SUMINISTRO E INSTALACIÓN. NO INCLUYE RELLENOS). NORMA CS207.' (delta -167.940.640) parece reemplazado por NP 'NP-07 - 6 DUCTOS D=6" PVC-TDP (INCLUYE SUMINISTRO E INSTALACIÓN. NO INCLUYE RELLENOS). NORMA CS212.' (delta 302.594.577). Sobrecosto neto 134.653.937.</t>
+  </si>
+  <si>
+    <t>489 / 551</t>
+  </si>
+  <si>
+    <t>H01-004</t>
+  </si>
+  <si>
+    <t>Posible reemplazo contractual-&gt;NP (filas 272 -&gt; 463)</t>
+  </si>
+  <si>
+    <t>Item contractual '5.044 - TUBERIA PVC U.M. EXT/INT LISO NORMA NTC 5070 D=39" (INCLUYE SUMINISTRO E INSTALACIÓN)' (delta -43.812.034) parece reemplazado por NP 'NP-17 - TUBERIA PVC U.M. EXT CORRUGADO/INT LISO U.M. NORMA NTC 3722-1 D=24" (INCLUYE SUMINISTRO E INSTALACIÓN)' (delta 141.000.499). Sobrecosto neto 97.188.465.</t>
+  </si>
+  <si>
+    <t>272 / 463</t>
+  </si>
+  <si>
+    <t>H06-01</t>
+  </si>
+  <si>
+    <t>Bloque de aceros (3.053M) fuera del total de obras vs bolsa fija F (2.978M): aclarar cuál rige</t>
+  </si>
+  <si>
+    <t>El bloque ACEROS (filas 680-687) suma 3.052.987.517 con AIU y reparte acero de refuerzo, acero liso y dovelas por CIV con cantidades actualizadas. Verificado con las fórmulas del libro: M688 = SUM(M8:M679) y CB688 = SUM(CB7:CB679)/2, por lo que el bloque NO está incluido en los 58.196.933.800 de obras; no hay doble conteo en el Excel. El acero se paga por la bolsa fija F (fila 697, 2.977.517.840), sin cambio desde V0. Diferencia bloque - bolsa: 75.469.677 (+2,5%). La memoria de la hoja Aceros muestra cantidades teóricas menores (~2.500M).</t>
+  </si>
+  <si>
+    <t>680-687 y 697</t>
+  </si>
+  <si>
+    <t>Pedir al contratista que aclare por escrito si el bloque ACEROS es la memoria de cantidades de la bolsa F o alcance adicional; en el primer caso, justificar la diferencia de 75.469.677 y confirmar que la bolsa alcanza; en el segundo, tramitarlo como adición. Dejar en el otrosí que el acero se paga únicamente por la bolsa F (o únicamente por ítems), nunca por ambos.</t>
+  </si>
+  <si>
+    <t>H01-012</t>
+  </si>
+  <si>
+    <t>Salto extremo de cantidad (I/H = 11.9861x) - fila 48</t>
+  </si>
+  <si>
+    <t>Item 3.006 'ESTABILIZACIÓN DE SUBRASANTE CON RAJÓN (SUMINISTRO, EXTENDIDO, NIVELACIÓN Y COMPACTACIÓN MANUAL)' paso de 44.0 a 527.39 M3. Impacto 68.652.015.</t>
+  </si>
+  <si>
+    <t>H01-009</t>
+  </si>
+  <si>
+    <t>Salto extremo de cantidad (I/H = 28.5588x) - fila 35</t>
+  </si>
+  <si>
+    <t>Item 2.004 'CORTE DE PAVIMENTO - INCLUYE EQUIPO: CORTADORA DE CONCRETO INCLUYE OPERARIO Y COMBUSTIBLE. INCLUYE DISCO DIAMANTADO ASFALTO-CONCRETO 350 MM, AGUA Y MANO DE OBRA' paso de 597.0 a 17049.629999999997 ML. Impacto 51.924.500.</t>
+  </si>
+  <si>
+    <t>H06-04</t>
+  </si>
+  <si>
+    <t>Bioseguridad no se actualiza a 8 meses pese a ser proporcional al plazo</t>
+  </si>
+  <si>
+    <t>El componente J Bioseguridad se mantiene en 59.390.312 (V0 = V4). Sin embargo la bioseguridad requiere insumos periodicos (elementos de proteccion personal, senalizacion, protocolos) que escalan con el tiempo. En un contrato ampliado 8 meses adicionales, tecnicamente deberia haber un incremento proporcional. El contratista no lo pidio.</t>
+  </si>
+  <si>
+    <t>699</t>
+  </si>
+  <si>
+    <t>Verificar si el contratista renuncia expresamente a solicitar adicion en bioseguridad para el plazo ampliado, o si esta consumiendo la bolsa vigente. Documentar la decision para evitar solicitudes posteriores no previstas.</t>
+  </si>
+  <si>
+    <t>H01-040</t>
+  </si>
+  <si>
+    <t>Discrepancias formulas O = (I-H) x L</t>
+  </si>
+  <si>
+    <t>1 renglones donde el balance mayores/menores O no coincide con (I-H)xL (&gt;$10 dif).</t>
+  </si>
+  <si>
+    <t>Solicitar aclaracion de que precio se uso para el balance de mayores/menores (VU visor vs VU contractual).</t>
+  </si>
+  <si>
+    <t>H02-200</t>
+  </si>
+  <si>
+    <t>CIV 16000017 outlier en md19_m2_por_m2 (2.79x mediana)</t>
+  </si>
+  <si>
+    <t>Ratio md19_m2_por_m2 = 0.1030, 2.79x sobre la mediana de los 27 CIVs.</t>
+  </si>
+  <si>
+    <t>Verificar en campo si la cantidad final del renglon corresponde al tramo real.</t>
+  </si>
+  <si>
+    <t>H02-201</t>
+  </si>
+  <si>
+    <t>CIV 16000024 outlier en md19_m2_por_m2 (2.65x mediana)</t>
+  </si>
+  <si>
+    <t>Ratio md19_m2_por_m2 = 0.0978, 2.65x sobre la mediana de los 27 CIVs.</t>
+  </si>
+  <si>
+    <t>H01-005</t>
+  </si>
+  <si>
+    <t>BAJA</t>
+  </si>
+  <si>
+    <t>Posible reemplazo contractual-&gt;NP (filas 269 -&gt; 464)</t>
+  </si>
+  <si>
+    <t>Item contractual '5.041 - TUBERIA PVC U.M. EXT/INT LISO NORMA NTC 5070 D=27" (INCLUYE SUMINISTRO E INSTALACIÓN)' (delta -88.567.080) parece reemplazado por NP 'NP-18 - TUBERIA PVC U.M. EXT CORRUGADO/INT LISO U.M. NORMA NTC 3722-1 D=27" (INCLUYE SUMINISTRO E INSTALACIÓN)' (delta 123.041.772). Sobrecosto neto 34.474.692.</t>
+  </si>
+  <si>
+    <t>269 / 464</t>
+  </si>
+  <si>
+    <t>H01-008</t>
+  </si>
+  <si>
+    <t>Salto extremo de cantidad (I/H = 37.0x) - fila 129</t>
+  </si>
+  <si>
+    <t>Item 5.007 'CODO HD 22.5° EXTREMO LISO PARA PVC D=6" (SUMINISTRO E INSTALACIÓN)' paso de 1.0 a 37.0 UN. Impacto 17.856.000.</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>H01-019</t>
+  </si>
+  <si>
+    <t>Variacion capitulo 4. SEÑALIZACIÓN Y DEMARCACIÓN: 0</t>
+  </si>
+  <si>
+    <t>4. SEÑALIZACIÓN Y DEMARCACIÓN: valor inicial 1.198.662.405 -&gt; final 1.198.662.405. Balance mayores/menores 0 + incorporacion NP 0.</t>
+  </si>
+  <si>
+    <t>H06-08</t>
+  </si>
+  <si>
+    <t>Fila 703 dice fecha 04-05-2026 pero el archivo es del 01-09-2026</t>
+  </si>
+  <si>
+    <t>La celda de la fila 703 rotula VALOR TOTAL CONTRATO PRESUPUESTO 04-05-2026 pero segun BRIEF y el nombre del archivo la version es del 01-09-2026. Es una etiqueta desactualizada.</t>
+  </si>
+  <si>
+    <t>703</t>
+  </si>
+  <si>
+    <t>Solicitar al contratista corregir la etiqueta de fecha para evitar confusion en revisiones futuras.</t>
+  </si>
+  <si>
+    <t>H-NP-06</t>
+  </si>
+  <si>
+    <t>INFO</t>
+  </si>
+  <si>
+    <t>22 NPs de V2 fueron eliminados en V4</t>
+  </si>
+  <si>
+    <t>Reduce en $924.318.412 (CD) frente a V2. Verificar si son NPs anulados o solo re-etiquetados.</t>
+  </si>
+  <si>
+    <t>Revisar en el balance de NPs anulados / rechazados que estos coincidan con los eliminados.</t>
+  </si>
+  <si>
+    <t>H03-01</t>
+  </si>
+  <si>
+    <t>Suma de obras con AIU por CIV cuadra a fila 688</t>
+  </si>
+  <si>
+    <t>Suma de it.civ[cid].valor (excluye ACEROS) = $58,196,933,869. Esperado (fila 688 col M) = $58,196,933,800. Δ = $69</t>
+  </si>
+  <si>
+    <t>688</t>
+  </si>
+  <si>
+    <t>Cuadre verificado; no requiere acción si Δ es residual (&lt;$1.000). Si es mayor, revisar redondeos por CIV.</t>
+  </si>
+  <si>
+    <t>H03-02</t>
+  </si>
+  <si>
+    <t>Suma total con componentes cuadra a fila 703</t>
+  </si>
+  <si>
+    <t>Obras+componentes por CIV = $75,426,575,268. Esperado = $75,426,575,199. Δ = $69</t>
+  </si>
+  <si>
+    <t>Cuadre verificado si Δ residual. En caso contrario, revisar reparto de componentes.</t>
+  </si>
+  <si>
+    <t>H01-041</t>
+  </si>
+  <si>
+    <t>Conciliacion global de obras OK</t>
+  </si>
+  <si>
+    <t>Inicial 44.303.294.799, final 58.196.933.800, delta 13.893.639.001.</t>
+  </si>
+  <si>
+    <t>totales</t>
+  </si>
+  <si>
+    <t>Sin observaciones.</t>
+  </si>
+  <si>
+    <t>H02-300</t>
+  </si>
+  <si>
+    <t>Mapeo especial CIV 500002375 = 16004876 = 50002375</t>
+  </si>
+  <si>
+    <t>El CIV V4 500002375 corresponde al tramo KR65 CL17-CL18 y se llama 16004876 en data.json, 16004876 en Hoja1 y 50002375 en MEMORIA CANTIDADES. Comparte segmento 91029906 con el CIV 16000047.</t>
+  </si>
+  <si>
+    <t>hoja principal + MEMORIA CANTIDADES + Hoja1</t>
+  </si>
+  <si>
+    <t>fila 3 IDs</t>
+  </si>
+  <si>
+    <t>Unificar la nomenclatura en documentos futuros (usar siempre el 500002375 IDU actual).</t>
+  </si>
+  <si>
     <t>H02</t>
   </si>
   <si>
     <t>Codigos IDU repetidos en la hoja principal (174)</t>
   </si>
   <si>
-    <t>Total duplicados: 174. Aparentes reubicaciones: 158. Duplicados reales: 16.</t>
-  </si>
-  <si>
-    <t>Revisar cada duplicado. Si son reubicaciones justificar el cambio de subcapitulo; si son sumas paralelas exigir consolidacion.</t>
-  </si>
-  <si>
-    <t>H03</t>
-  </si>
-  <si>
-    <t>VU V4 desviado &gt;2% del PRESUPUESTO CONTRACTUAL (367 items)</t>
-  </si>
-  <si>
-    <t>Top: 4878 70.52%, 4878 70.52%, 4878 70.52%, 4878 70.52%, 8406 42.0%</t>
-  </si>
-  <si>
-    <t>Verificar autorizacion de cambio de VU respecto al contrato firmado. Los VU deben coincidir con el contractual.</t>
-  </si>
-  <si>
-    <t>H06-05</t>
-  </si>
-  <si>
-    <t>MEDIA</t>
-  </si>
-  <si>
-    <t>Salto V3 (63MM, 3 meses) a V4 (75MM, 8 meses) implica delta de $11.677M</t>
-  </si>
-  <si>
-    <t>En 4 meses (mayo a septiembre 2026) el presupuesto adicional pedido paso de $4.323M (V3) a $16.000M (V4), un incremento de $11.677M. El 88,7% del delta se explica por obras (+$10.361M) y el 11,3% por escalar SST/PGS/PMT de 3 a 8 meses. Los VU (precios unitarios) son practicamente identicos entre V3 y V4, por lo que el delta es efecto CANTIDAD y NPs, no efecto PRECIO.</t>
-  </si>
-  <si>
-    <t>PRESUPUESTO 63 mm vs PRESUPUESTO TODOS LOS CIV 84 NP</t>
-  </si>
-  <si>
-    <t>657 y 692</t>
-  </si>
-  <si>
-    <t>Solicitar al contratista la sustentacion tecnica del incremento de $10.361M en obras entre V3 y V4: (1) que items se incorporaron o crecieron; (2) que NPs se agregaron; (3) por que no se identificaron en V3 (mayo 2026) y aparecen 4 meses despues. Verificar contra memorias de cantidades y bitacora de obra.</t>
-  </si>
-  <si>
-    <t>H06-06</t>
-  </si>
-  <si>
-    <t>El Fondo de Compensaciones aparecio en V2 y desaparecio en V4 sin trazabilidad</t>
-  </si>
-  <si>
-    <t>V2 (Alt 1, 21-04-2026) incluyo un Fondo de Compensaciones de 5.942.657.520 que no existe ni en V0 ni en V4. En V3 y V4 vuelve a 0. No hay comunicacion oficial que explique el origen ni el motivo de su retiro. Podria estar relacionado con compensaciones ambientales/arqueologicas que se movieron a los NP-109 y NP-110 (arqueologia GLB/MES) que aparecen ahora dentro de obras.</t>
-  </si>
-  <si>
-    <t>704</t>
-  </si>
-  <si>
-    <t>Solicitar al contratista trazabilidad documental del Fondo de Compensaciones: (1) que compensaciones especificas se planeaban financiar; (2) por que se retiraron; (3) verificar que no se este pagando doble via NPs de arqueologia u otros.</t>
-  </si>
-  <si>
-    <t>H02-001</t>
-  </si>
-  <si>
-    <t>Reparto de la linea base por CIV no publicado por el contratista</t>
-  </si>
-  <si>
-    <t>La col N del Excel suma $44,303,294,799 de valor inicial con AIU global. La reconstruccion por CIV (multiplicando cantidad_inicial_data_json * VU actualizado L) suma $41,842,985,108 (delta $-2,460,309,691). El Excel no reparte la cantidad contractual (col H) por CIV, por lo que la linea base por CIV se estima con data.json (contrato firmado); es un pixel-perfect solo para los ítems que mantuvieron el codigo_idu.</t>
-  </si>
-  <si>
-    <t>col H (linea base) vs bloque S:BW (matriz por CIV)</t>
-  </si>
-  <si>
-    <t>Pedir al contratista el reparto oficial de la cantidad contractual por CIV (col H desagregada) para auditar al peso el Delta por CIV.</t>
-  </si>
-  <si>
-    <t>H03-NP-16000010</t>
-  </si>
-  <si>
-    <t>CIV 16000010: 58.45% del valor viene de NPs</t>
-  </si>
-  <si>
-    <t>Contractual $1,641,253,281 + NP $2,308,849,811 = obras totales. Alta dependencia de precios no pactados.</t>
-  </si>
-  <si>
-    <t>Auditar NPs asignados a este CIV, verificar códigos IDU, análisis de precios unitarios y actas de fijación.</t>
-  </si>
-  <si>
-    <t>H04</t>
-  </si>
-  <si>
-    <t>Inconsistencia entre hojas (2)</t>
-  </si>
-  <si>
-    <t>Totales no coinciden entre hojas de resumen y la hoja principal.</t>
-  </si>
-  <si>
-    <t>Alinear hojas resumen/EJECUTIVO/Presupuesto estimado con el total final $75.426.575.199.</t>
-  </si>
-  <si>
-    <t>H01-007</t>
-  </si>
-  <si>
-    <t>Salto extremo de cantidad (I/H = 39.9949x) - fila 73</t>
-  </si>
-  <si>
-    <t>Item 3.027 'SARDINEL FUNDIDO EN SITIO EN CONCRETO PREMEZCLADO DE 3000PSI. SUMINISTRO Y CONSTRUCCION. (GRAVA COMÚN) E=0.20M H=0.35M (INCLUYE FORMALETA METÁLICA, ACERO DE REFUERZO Y ALAMBRE NEGRO).' paso de 141.0 a 5639.28 ML. Impacto 413.740.072.</t>
-  </si>
-  <si>
-    <t>H01-018</t>
-  </si>
-  <si>
-    <t>Variacion capitulo 7. DESVÍOS: -326.577.225</t>
-  </si>
-  <si>
-    <t>7. DESVÍOS: valor inicial 326.577.225 -&gt; final 0. Balance mayores/menores -326.577.225 + incorporacion NP 0.</t>
-  </si>
-  <si>
-    <t>H01-003</t>
-  </si>
-  <si>
-    <t>Posible reemplazo contractual-&gt;NP (filas 489 -&gt; 551)</t>
-  </si>
-  <si>
-    <t>Item contractual '6.006 - 2 DUCTOS D=3" PVC-EB (INCLUYE SUMINISTRO E INSTALACIÓN. NO INCLUYE RELLENOS). NORMA CS207.' (delta -167.940.640) parece reemplazado por NP 'NP-07 - 6 DUCTOS D=6" PVC-TDP (INCLUYE SUMINISTRO E INSTALACIÓN. NO INCLUYE RELLENOS). NORMA CS212.' (delta 302.594.577). Sobrecosto neto 134.653.937.</t>
-  </si>
-  <si>
-    <t>489 / 551</t>
-  </si>
-  <si>
-    <t>H01-004</t>
-  </si>
-  <si>
-    <t>Posible reemplazo contractual-&gt;NP (filas 272 -&gt; 463)</t>
-  </si>
-  <si>
-    <t>Item contractual '5.044 - TUBERIA PVC U.M. EXT/INT LISO NORMA NTC 5070 D=39" (INCLUYE SUMINISTRO E INSTALACIÓN)' (delta -43.812.034) parece reemplazado por NP 'NP-17 - TUBERIA PVC U.M. EXT CORRUGADO/INT LISO U.M. NORMA NTC 3722-1 D=24" (INCLUYE SUMINISTRO E INSTALACIÓN)' (delta 141.000.499). Sobrecosto neto 97.188.465.</t>
-  </si>
-  <si>
-    <t>272 / 463</t>
-  </si>
-  <si>
-    <t>H01-012</t>
-  </si>
-  <si>
-    <t>Salto extremo de cantidad (I/H = 11.9861x) - fila 48</t>
-  </si>
-  <si>
-    <t>Item 3.006 'ESTABILIZACIÓN DE SUBRASANTE CON RAJÓN (SUMINISTRO, EXTENDIDO, NIVELACIÓN Y COMPACTACIÓN MANUAL)' paso de 44.0 a 527.39 M3. Impacto 68.652.015.</t>
-  </si>
-  <si>
-    <t>H01-009</t>
-  </si>
-  <si>
-    <t>Salto extremo de cantidad (I/H = 28.5588x) - fila 35</t>
-  </si>
-  <si>
-    <t>Item 2.004 'CORTE DE PAVIMENTO - INCLUYE EQUIPO: CORTADORA DE CONCRETO INCLUYE OPERARIO Y COMBUSTIBLE. INCLUYE DISCO DIAMANTADO ASFALTO-CONCRETO 350 MM, AGUA Y MANO DE OBRA' paso de 597.0 a 17049.629999999997 ML. Impacto 51.924.500.</t>
-  </si>
-  <si>
-    <t>H06-04</t>
-  </si>
-  <si>
-    <t>Bioseguridad no se actualiza a 8 meses pese a ser proporcional al plazo</t>
-  </si>
-  <si>
-    <t>El componente J Bioseguridad se mantiene en 59.390.312 (V0 = V4). Sin embargo la bioseguridad requiere insumos periodicos (elementos de proteccion personal, senalizacion, protocolos) que escalan con el tiempo. En un contrato ampliado 8 meses adicionales, tecnicamente deberia haber un incremento proporcional. El contratista no lo pidio.</t>
-  </si>
-  <si>
-    <t>703</t>
-  </si>
-  <si>
-    <t>Verificar si el contratista renuncia expresamente a solicitar adicion en bioseguridad para el plazo ampliado, o si esta consumiendo la bolsa vigente. Documentar la decision para evitar solicitudes posteriores no previstas.</t>
-  </si>
-  <si>
-    <t>H01-040</t>
-  </si>
-  <si>
-    <t>Discrepancias formulas O = (I-H) x L</t>
-  </si>
-  <si>
-    <t>1 renglones donde el balance mayores/menores O no coincide con (I-H)xL (&gt;$10 dif).</t>
-  </si>
-  <si>
-    <t>Solicitar aclaracion de que precio se uso para el balance de mayores/menores (VU visor vs VU contractual).</t>
-  </si>
-  <si>
-    <t>H02-200</t>
-  </si>
-  <si>
-    <t>CIV 16000017 outlier en md19_m2_por_m2 (2.79x mediana)</t>
-  </si>
-  <si>
-    <t>Ratio md19_m2_por_m2 = 0.1030, 2.79x sobre la mediana de los 27 CIVs.</t>
-  </si>
-  <si>
-    <t>Verificar en campo si la cantidad final del renglon corresponde al tramo real.</t>
-  </si>
-  <si>
-    <t>H02-201</t>
-  </si>
-  <si>
-    <t>CIV 16000024 outlier en md19_m2_por_m2 (2.65x mediana)</t>
-  </si>
-  <si>
-    <t>Ratio md19_m2_por_m2 = 0.0978, 2.65x sobre la mediana de los 27 CIVs.</t>
-  </si>
-  <si>
-    <t>H01-005</t>
-  </si>
-  <si>
-    <t>BAJA</t>
-  </si>
-  <si>
-    <t>Posible reemplazo contractual-&gt;NP (filas 269 -&gt; 464)</t>
-  </si>
-  <si>
-    <t>Item contractual '5.041 - TUBERIA PVC U.M. EXT/INT LISO NORMA NTC 5070 D=27" (INCLUYE SUMINISTRO E INSTALACIÓN)' (delta -88.567.080) parece reemplazado por NP 'NP-18 - TUBERIA PVC U.M. EXT CORRUGADO/INT LISO U.M. NORMA NTC 3722-1 D=27" (INCLUYE SUMINISTRO E INSTALACIÓN)' (delta 123.041.772). Sobrecosto neto 34.474.692.</t>
-  </si>
-  <si>
-    <t>269 / 464</t>
-  </si>
-  <si>
-    <t>H01-008</t>
-  </si>
-  <si>
-    <t>Salto extremo de cantidad (I/H = 37.0x) - fila 129</t>
-  </si>
-  <si>
-    <t>Item 5.007 'CODO HD 22.5° EXTREMO LISO PARA PVC D=6" (SUMINISTRO E INSTALACIÓN)' paso de 1.0 a 37.0 UN. Impacto 17.856.000.</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>H01-019</t>
-  </si>
-  <si>
-    <t>Variacion capitulo 4. SEÑALIZACIÓN Y DEMARCACIÓN: 0</t>
-  </si>
-  <si>
-    <t>4. SEÑALIZACIÓN Y DEMARCACIÓN: valor inicial 1.198.662.405 -&gt; final 1.198.662.405. Balance mayores/menores 0 + incorporacion NP 0.</t>
-  </si>
-  <si>
-    <t>H06-08</t>
-  </si>
-  <si>
-    <t>Fila 707 dice fecha 04-05-2026 pero el archivo es del 01-09-2026</t>
-  </si>
-  <si>
-    <t>La celda de la fila 707 rotula VALOR TOTAL CONTRATO PRESUPUESTO 04-05-2026 pero segun BRIEF y el nombre del archivo la version es del 01-09-2026. Es una etiqueta desactualizada.</t>
-  </si>
-  <si>
-    <t>707</t>
-  </si>
-  <si>
-    <t>Solicitar al contratista corregir la etiqueta de fecha para evitar confusion en revisiones futuras.</t>
-  </si>
-  <si>
-    <t>H-NP-06</t>
-  </si>
-  <si>
-    <t>INFO</t>
-  </si>
-  <si>
-    <t>22 NPs de V2 fueron eliminados en V4</t>
-  </si>
-  <si>
-    <t>Reduce en $924.318.412 (CD) frente a V2. Verificar si son NPs anulados o solo re-etiquetados.</t>
-  </si>
-  <si>
-    <t>Revisar en el balance de NPs anulados / rechazados que estos coincidan con los eliminados.</t>
-  </si>
-  <si>
-    <t>H03-01</t>
-  </si>
-  <si>
-    <t>Suma de obras con AIU por CIV cuadra a fila 688</t>
-  </si>
-  <si>
-    <t>Suma de it.civ[cid].valor (excluye ACEROS) = $58,196,933,869. Esperado (fila 688 col M) = $58,196,933,800. Δ = $69</t>
-  </si>
-  <si>
-    <t>688</t>
-  </si>
-  <si>
-    <t>Cuadre verificado; no requiere acción si Δ es residual (&lt;$1.000). Si es mayor, revisar redondeos por CIV.</t>
-  </si>
-  <si>
-    <t>H03-02</t>
-  </si>
-  <si>
-    <t>Suma total con componentes cuadra a fila 703</t>
-  </si>
-  <si>
-    <t>Obras+componentes por CIV = $75,426,575,268. Esperado = $75,426,575,199. Δ = $69</t>
-  </si>
-  <si>
-    <t>Cuadre verificado si Δ residual. En caso contrario, revisar reparto de componentes.</t>
-  </si>
-  <si>
-    <t>H01-041</t>
-  </si>
-  <si>
-    <t>Conciliacion global de obras OK</t>
-  </si>
-  <si>
-    <t>Inicial 44.303.294.799, final 58.196.933.800, delta 13.893.639.001.</t>
-  </si>
-  <si>
-    <t>totales</t>
-  </si>
-  <si>
-    <t>Sin observaciones.</t>
-  </si>
-  <si>
-    <t>H02-300</t>
-  </si>
-  <si>
-    <t>Mapeo especial CIV 500002375 = 16004876 = 50002375</t>
-  </si>
-  <si>
-    <t>El CIV V4 500002375 corresponde al tramo KR65 CL17-CL18 y se llama 16004876 en data.json, 16004876 en Hoja1 y 50002375 en MEMORIA CANTIDADES. Comparte segmento 91029906 con el CIV 16000047.</t>
-  </si>
-  <si>
-    <t>hoja principal + MEMORIA CANTIDADES + Hoja1</t>
-  </si>
-  <si>
-    <t>fila 3 IDs</t>
-  </si>
-  <si>
-    <t>Unificar la nomenclatura en documentos futuros (usar siempre el 500002375 IDU actual).</t>
+    <t>Total codigos con mas de un renglon: 174. En subcapitulos distintos (estructura item x subcapitulo, p. ej. IDU vs ESP): 174. Duplicados reales en el mismo subcapitulo: 0. No implican doble suma: cada renglon tiene su propia cantidad. Si afectan el cruce con V1/V2, que se hace por codigo agregado (ver limitaciones del registro de auditoria).</t>
+  </si>
+  <si>
+    <t>Pedir al contratista la conciliacion de los codigos que pasan de un subcapitulo a otro (reubicaciones, seccion I de la app); si hay duplicados en el mismo subcapitulo, exigir consolidacion.</t>
+  </si>
+  <si>
+    <t>H05</t>
+  </si>
+  <si>
+    <t>Consistencia entre hojas OK (3 diferencias explicadas)</t>
+  </si>
+  <si>
+    <t>Los totales de resumen, EJECUTIVO y Presupuesto estimado coinciden con la hoja principal. Diferencias explicadas: Presupuesto estimado!A11 = 74.667.840.865 (Excluye 'VALOR ESTIMADO DE FASE DE OBRAS INICIALES' (M701 = 758.734.334); la etiqueta A10 lo dice: valor para la etapa de construccion.); EJECUTIVO!I45 = 58.196.933.869 (Diferencia de redondeo: la hoja EJECUTIVO suma los 27 CIV redondeados uno a uno (ROUND por CIV) y la hoja principal redondea el total del renglon.); EJECUTIVO!I56 = 75.426.575.268 (Diferencia de redondeo: la hoja EJECUTIVO suma los 27 CIV redondeados uno a uno (ROUND por CIV) y la hoja principal redondea el total del renglon.)</t>
+  </si>
+  <si>
+    <t>Sin accion. La hoja EJECUTIVO conserva el encabezado 11/05/2026: pedir que se actualice a la fecha del radicado.</t>
   </si>
   <si>
     <t>H06-07</t>
@@ -4788,10 +4806,10 @@
     <t>AIU diferenciado por componente confirmado por presupuesto</t>
   </si>
   <si>
-    <t>El presupuesto aplica AIU 31,849% a obras+redes+acero (contractual), AIU 20,006% a PMA-SST y AIU 19,566% a Dialogo y PMT. La diferenciacion esta documentada en las filas 740 del detalle SST y es coherente con las cartillas IDU: el AIU pleno solo aplica a costos directos de obra civil.</t>
-  </si>
-  <si>
-    <t>740</t>
+    <t>El presupuesto aplica AIU 31,849% a obras+redes+acero (contractual), AIU 20,006% a PMA-SST y AIU 19,566% a Dialogo y PMT. La diferenciacion esta documentada en las filas 736 del detalle SST y es coherente con las cartillas IDU: el AIU pleno solo aplica a costos directos de obra civil.</t>
+  </si>
+  <si>
+    <t>736</t>
   </si>
   <si>
     <t>Documentar en informe mensual de Interventoria los tres AIU diferenciados para claridad ante IDU.</t>
@@ -44817,7 +44835,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -44934,265 +44952,265 @@
         <v>1323</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1312</v>
+        <v>1324</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H4" s="4">
-        <v>6777852537</v>
+        <v>15086222761</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H5" s="4">
-        <v>5899197969</v>
+        <v>6777852537</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1327</v>
+        <v>1334</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1330</v>
+        <v>1337</v>
       </c>
       <c r="H6" s="4">
-        <v>3950103092</v>
+        <v>5899197969</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1331</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="H7" s="4">
-        <v>3672527262</v>
+        <v>3950103092</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1321</v>
+        <v>1343</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1324</v>
+        <v>1346</v>
       </c>
       <c r="H8" s="4">
-        <v>3556107781</v>
+        <v>3672527262</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1325</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>934</v>
+        <v>1331</v>
       </c>
       <c r="H9" s="4">
-        <v>3269600612</v>
+        <v>3556107781</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1347</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1309</v>
+        <v>1328</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1351</v>
+        <v>934</v>
       </c>
       <c r="H10" s="4">
-        <v>2977517840</v>
+        <v>3269600612</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1324</v>
+        <v>1331</v>
       </c>
       <c r="H11" s="4">
         <v>2787734305</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1325</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1327</v>
+        <v>1334</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1330</v>
+        <v>1337</v>
       </c>
       <c r="H12" s="4">
         <v>2767058972</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1331</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>1312</v>
@@ -45204,24 +45222,24 @@
         <v>-2584929953</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>1312</v>
@@ -45233,24 +45251,24 @@
         <v>-2584929953</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>1312</v>
@@ -45262,24 +45280,24 @@
         <v>2518521916</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1347</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>1312</v>
@@ -45291,24 +45309,24 @@
         <v>2348873855</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>1312</v>
@@ -45320,82 +45338,82 @@
         <v>2348873855</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="H18" s="4">
         <v>-1883363119</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="H19" s="4">
         <v>1879745340</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1347</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>1312</v>
@@ -45407,24 +45425,24 @@
         <v>-1811267958</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>1312</v>
@@ -45436,82 +45454,82 @@
         <v>-1811267958</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1336</v>
+        <v>1343</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1339</v>
+        <v>1346</v>
       </c>
       <c r="H22" s="4">
         <v>1658490306</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="2" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1324</v>
+        <v>1331</v>
       </c>
       <c r="H23" s="4">
         <v>1613831550</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1325</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>1312</v>
@@ -45523,24 +45541,24 @@
         <v>1542541484</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>1312</v>
@@ -45552,82 +45570,82 @@
         <v>1542541484</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="2" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1336</v>
+        <v>1343</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1339</v>
+        <v>1346</v>
       </c>
       <c r="H26" s="4">
         <v>1325793518</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="2" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1336</v>
+        <v>1343</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1339</v>
+        <v>1346</v>
       </c>
       <c r="H27" s="4">
         <v>1321707331</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="2" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>1312</v>
@@ -45639,314 +45657,314 @@
         <v>1107150225</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1347</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="2" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="H29" s="4">
         <v>-1059297570</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="2" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="H30" s="4">
         <v>-1059297570</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="2" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="H31" s="4">
         <v>-840308079</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="2" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="H32" s="4">
         <v>-840308079</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="2" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1336</v>
+        <v>1343</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1339</v>
+        <v>1346</v>
       </c>
       <c r="H33" s="4">
         <v>801161445</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="2" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="H34" s="4">
         <v>778412250</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1347</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="2" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="H35" s="4">
         <v>707253958</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="2" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="H36" s="4">
         <v>684670659</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="2" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="H37" s="4">
         <v>-671669280</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="2" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="H38" s="4">
         <v>-671669280</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="2" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>1312</v>
@@ -45958,24 +45976,24 @@
         <v>-661011828</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="2" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>1312</v>
@@ -45987,24 +46005,24 @@
         <v>660384913</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="2" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>1312</v>
@@ -46016,82 +46034,82 @@
         <v>660384913</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="2" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="H42" s="4">
         <v>528386445.5799817</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="2" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1324</v>
+        <v>1331</v>
       </c>
       <c r="H43" s="4">
         <v>-515309947</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>1325</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="2" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1468</v>
+        <v>1321</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>1312</v>
@@ -46103,24 +46121,24 @@
         <v>172434</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="2" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>1308</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1468</v>
+        <v>1321</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>1312</v>
@@ -46130,150 +46148,152 @@
         <v>0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="2" t="s">
-        <v>1476</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>1308</v>
+        <v>1477</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>1478</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1468</v>
+        <v>1309</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>1312</v>
-      </c>
-      <c r="G46" s="2"/>
+        <v>1481</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>1482</v>
+      </c>
       <c r="H46" s="4">
-        <v>0</v>
+        <v>11677108105</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="2" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>1309</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>1484</v>
+        <v>1312</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="H47" s="4">
-        <v>11677108105</v>
+        <v>5942657520</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="2" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1309</v>
+        <v>1343</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="H48" s="4">
-        <v>5942657520</v>
+        <v>2460309691</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="2" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1495</v>
+        <v>1337</v>
       </c>
       <c r="H49" s="4">
-        <v>2460309691</v>
+        <v>2308849811</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="2" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1330</v>
+        <v>965</v>
       </c>
       <c r="H50" s="4">
-        <v>2308849811</v>
+        <v>413740072</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1500</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -46281,10 +46301,10 @@
         <v>1501</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1468</v>
+        <v>1328</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>1502</v>
@@ -46292,42 +46312,46 @@
       <c r="E51" s="2" t="s">
         <v>1503</v>
       </c>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
+      <c r="F51" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>1331</v>
+      </c>
       <c r="H51" s="4">
-        <v>1988375733</v>
+        <v>-326577225</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1504</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>1505</v>
       </c>
-      <c r="B52" s="11" t="s">
-        <v>1481</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>1506</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>1507</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>965</v>
+        <v>1507</v>
       </c>
       <c r="H52" s="4">
-        <v>413740072</v>
+        <v>134653937</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1373</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -46335,10 +46359,10 @@
         <v>1508</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>1509</v>
@@ -46350,537 +46374,560 @@
         <v>1312</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1324</v>
+        <v>1511</v>
       </c>
       <c r="H53" s="4">
-        <v>-326577225</v>
+        <v>97188465</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>1325</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="2" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="H54" s="4">
-        <v>134653937</v>
+        <v>75469677</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1437</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="2" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1518</v>
+        <v>1020</v>
       </c>
       <c r="H55" s="4">
-        <v>97188465</v>
+        <v>68652015</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>1437</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="2" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="H56" s="4">
-        <v>68652015</v>
+        <v>51924500</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="2" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1030</v>
+        <v>1526</v>
       </c>
       <c r="H57" s="4">
-        <v>51924500</v>
+        <v>40000000</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1373</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="2" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1309</v>
+        <v>1328</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1528</v>
+        <v>939</v>
       </c>
       <c r="H58" s="4">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="2" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1321</v>
+        <v>1343</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>939</v>
+        <v>1346</v>
       </c>
       <c r="H59" s="4">
         <v>0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="2" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1336</v>
+        <v>1343</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1339</v>
+        <v>1346</v>
       </c>
       <c r="H60" s="4">
         <v>0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="2" t="s">
-        <v>1538</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>1481</v>
+        <v>1539</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>1540</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1339</v>
+        <v>1543</v>
       </c>
       <c r="H61" s="4">
-        <v>0</v>
+        <v>34474692</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1537</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="2" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="H62" s="4">
-        <v>34474692</v>
+        <v>17856000</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1437</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="2" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1549</v>
+        <v>1331</v>
       </c>
       <c r="H63" s="4">
-        <v>17856000</v>
+        <v>0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>1373</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="2" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1324</v>
+        <v>1554</v>
       </c>
       <c r="H64" s="4">
         <v>0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>1325</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="2" t="s">
-        <v>1553</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>1542</v>
+        <v>1556</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>1557</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1309</v>
+        <v>1461</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>1556</v>
-      </c>
+      <c r="G65" s="2"/>
       <c r="H65" s="4">
-        <v>0</v>
+        <v>-924318412</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="2" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1459</v>
+        <v>1334</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="G66" s="2"/>
+      <c r="G66" s="2" t="s">
+        <v>1564</v>
+      </c>
       <c r="H66" s="4">
-        <v>-924318412</v>
+        <v>69</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="2" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1327</v>
+        <v>1334</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1566</v>
+        <v>1554</v>
       </c>
       <c r="H67" s="4">
         <v>69</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="2" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1528</v>
+        <v>1573</v>
       </c>
       <c r="H68" s="4">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>1571</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="2" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1321</v>
+        <v>1343</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1573</v>
+        <v>1576</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>1312</v>
+        <v>1578</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="H69" s="4">
         <v>0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="2" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1336</v>
+        <v>1321</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>1580</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>1581</v>
-      </c>
+        <v>1312</v>
+      </c>
+      <c r="G70" s="2"/>
       <c r="H70" s="4">
         <v>0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="2" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="C71" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>1586</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="4">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="2" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>1309</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>1584</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>1585</v>
-      </c>
-      <c r="F71" s="2" t="s">
+      <c r="D72" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>1586</v>
-      </c>
-      <c r="H71" s="4">
-        <v>0</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>1587</v>
+      <c r="G72" s="2" t="s">
+        <v>1592</v>
+      </c>
+      <c r="H72" s="4">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>1593</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I71"/>
+  <autoFilter ref="A1:I72"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/analisis/Analisis_Presupuesto_2026-09.xlsx
+++ b/analisis/Analisis_Presupuesto_2026-09.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Costo por CIV'!$A$1:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hallazgos!$A$1:$I$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hallazgos!$A$1:$I$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">NPs!$A$1:$L$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Variación neta por código'!$A$1:$F$267</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Variación por CIV'!$A$1:$N$28</definedName>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5388" uniqueCount="1594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5412" uniqueCount="1603">
   <si>
     <t>Análisis Presupuesto 01-09-2026 · 75MM · 8 meses</t>
   </si>
@@ -4632,10 +4632,10 @@
     <t>H02-200</t>
   </si>
   <si>
-    <t>CIV 16000017 outlier en md19_m2_por_m2 (2.79x mediana)</t>
-  </si>
-  <si>
-    <t>Ratio md19_m2_por_m2 = 0.1030, 2.79x sobre la mediana de los 27 CIVs.</t>
+    <t>CIV 16000013: intensidad de andén (m²/m²) 5,49× la mediana</t>
+  </si>
+  <si>
+    <t>Ratio anden_m2_por_m2 = 1.2087, 5.49x sobre la mediana de los 27 CIVs.</t>
   </si>
   <si>
     <t>Verificar en campo si la cantidad final del renglon corresponde al tramo real.</t>
@@ -4644,10 +4644,37 @@
     <t>H02-201</t>
   </si>
   <si>
-    <t>CIV 16000024 outlier en md19_m2_por_m2 (2.65x mediana)</t>
-  </si>
-  <si>
-    <t>Ratio md19_m2_por_m2 = 0.0978, 2.65x sobre la mediana de los 27 CIVs.</t>
+    <t>CIV 16000017: intensidad de andén (m²/m²) 3,82× la mediana</t>
+  </si>
+  <si>
+    <t>Ratio anden_m2_por_m2 = 0.8416, 3.82x sobre la mediana de los 27 CIVs.</t>
+  </si>
+  <si>
+    <t>H02-202</t>
+  </si>
+  <si>
+    <t>CIV 16000024: intensidad de andén (m²/m²) 3,33× la mediana</t>
+  </si>
+  <si>
+    <t>Ratio anden_m2_por_m2 = 0.7324, 3.33x sobre la mediana de los 27 CIVs.</t>
+  </si>
+  <si>
+    <t>H02-203</t>
+  </si>
+  <si>
+    <t>CIV 16000017: intensidad de rajón (m³/m²) 2,79× la mediana</t>
+  </si>
+  <si>
+    <t>Ratio rajon_m3_por_m2 = 0.7208, 2.79x sobre la mediana de los 27 CIVs.</t>
+  </si>
+  <si>
+    <t>H02-204</t>
+  </si>
+  <si>
+    <t>CIV 16000017: intensidad de mezcla asfáltica MD12+MD19 (m³/m²) 2,79× la mediana</t>
+  </si>
+  <si>
+    <t>Ratio mezcla_asfaltica_md12_md19_m3_por_m2 = 0.1030, 2.79x sobre la mediana de los 27 CIVs.</t>
   </si>
   <si>
     <t>H01-005</t>
@@ -44835,7 +44862,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -46590,344 +46617,431 @@
       <c r="A61" s="2" t="s">
         <v>1539</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="11" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>1540</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>1328</v>
-      </c>
-      <c r="D61" s="2" t="s">
+      <c r="E61" s="2" t="s">
         <v>1541</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>1542</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1543</v>
+        <v>1346</v>
       </c>
       <c r="H61" s="4">
-        <v>34474692</v>
+        <v>0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1439</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>1544</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>1328</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>1545</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>1546</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1547</v>
+        <v>1346</v>
       </c>
       <c r="H62" s="4">
-        <v>17856000</v>
+        <v>0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1375</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="2" t="s">
-        <v>1548</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>1540</v>
+        <v>1545</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>1478</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1328</v>
+        <v>1343</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1331</v>
+        <v>1346</v>
       </c>
       <c r="H63" s="4">
         <v>0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>1332</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>1551</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>1309</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>1552</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>1553</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="H64" s="4">
-        <v>0</v>
+        <v>34474692</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>1555</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="2" t="s">
-        <v>1556</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>1557</v>
+        <v>1553</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>1549</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1461</v>
+        <v>1328</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="G65" s="2"/>
+      <c r="G65" s="2" t="s">
+        <v>1556</v>
+      </c>
       <c r="H65" s="4">
-        <v>-924318412</v>
+        <v>17856000</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>1560</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="2" t="s">
-        <v>1561</v>
-      </c>
-      <c r="B66" s="13" t="s">
         <v>1557</v>
       </c>
+      <c r="B66" s="12" t="s">
+        <v>1549</v>
+      </c>
       <c r="C66" s="2" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1563</v>
+        <v>1559</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1564</v>
+        <v>1331</v>
       </c>
       <c r="H66" s="4">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1565</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="2" t="s">
-        <v>1566</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>1557</v>
+        <v>1560</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>1549</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1334</v>
+        <v>1309</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>1312</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1554</v>
+        <v>1563</v>
       </c>
       <c r="H67" s="4">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="2" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>1557</v>
+        <v>1566</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1328</v>
+        <v>1461</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1571</v>
+        <v>1567</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="G68" s="2" t="s">
-        <v>1573</v>
-      </c>
+      <c r="G68" s="2"/>
       <c r="H68" s="4">
-        <v>0</v>
+        <v>-924318412</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>1574</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="2" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>1557</v>
+        <v>1566</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1343</v>
+        <v>1334</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>1578</v>
+        <v>1312</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="H69" s="4">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="2" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>1557</v>
+        <v>1566</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1321</v>
+        <v>1334</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="G70" s="2"/>
+      <c r="G70" s="2" t="s">
+        <v>1563</v>
+      </c>
       <c r="H70" s="4">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>1584</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="2" t="s">
-        <v>1585</v>
+        <v>1579</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>1557</v>
+        <v>1566</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1587</v>
-      </c>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
+        <v>1581</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>1582</v>
+      </c>
       <c r="H71" s="4">
         <v>0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>1588</v>
+      </c>
+      <c r="H72" s="4">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="s">
         <v>1589</v>
       </c>
-      <c r="B72" s="13" t="s">
-        <v>1557</v>
-      </c>
-      <c r="C72" s="2" t="s">
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G73" s="2"/>
+      <c r="H73" s="4">
+        <v>0</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="4">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>1309</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F72" s="2" t="s">
+      <c r="D75" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="G72" s="2" t="s">
-        <v>1592</v>
-      </c>
-      <c r="H72" s="4">
-        <v>0</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>1593</v>
+      <c r="G75" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="H75" s="4">
+        <v>0</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>1602</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I72"/>
+  <autoFilter ref="A1:I75"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>